--- a/data/prijzen.xlsx
+++ b/data/prijzen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icthva.sharepoint.com/sites/FT_O_URAN_Urban_Analytics_Team-KIACECBM/Gedeelde documenten/KIA CE CBM/KIA CE CMS_Project/WP1_Datacollectie - Vormen database, meeteenheden en toekomstscenario’s/data prototype/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\GitHub\FLIM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="930" documentId="11_4A680A51338CB84F137C08446651AA06411C1836" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D614A637-BF6B-4191-9526-415939FFDD99}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C98342-EC17-427A-95D8-132BC2EE9ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datasheet 260218 (def)" sheetId="6" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>Leer</t>
-  </si>
-  <si>
-    <t>Plastics algemeen</t>
   </si>
   <si>
     <t>Hout Algemeen</t>
@@ -232,12 +229,6 @@
     <t>Gerecycled metaal (niet genormaliseerd)</t>
   </si>
   <si>
-    <t>Gerecycled metaal</t>
-  </si>
-  <si>
-    <t>Gerecycled schuim</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -312,6 +303,21 @@
   <si>
     <t>LET OP: gemiddelde van 2016 en 2018; door omstandigheden geen data</t>
   </si>
+  <si>
+    <t>PVC (zacht)</t>
+  </si>
+  <si>
+    <t>Kunststof algemeen</t>
+  </si>
+  <si>
+    <t>Kunststof (gerecycled)</t>
+  </si>
+  <si>
+    <t>Metaal (gerecycled)</t>
+  </si>
+  <si>
+    <t>Schuim (gerecycled)</t>
+  </si>
 </sst>
 </file>
 
@@ -325,7 +331,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,7 +557,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -677,7 +683,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -689,10 +694,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Komma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{383758C4-BEE1-4B9D-897A-94EA73C0E624}"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Valuta" xfId="2" builtinId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1033,29 +1038,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3789D834-1515-4BFD-9B55-AA63AD191663}">
   <dimension ref="A1:BO137"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="24" customWidth="1"/>
-    <col min="4" max="5" width="9.140625" style="24"/>
-    <col min="6" max="8" width="13.85546875" style="25" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="24" customWidth="1"/>
+    <col min="4" max="5" width="9.109375" style="24"/>
+    <col min="6" max="8" width="13.88671875" style="25" customWidth="1"/>
     <col min="9" max="9" width="19" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" style="25" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="25" customWidth="1"/>
-    <col min="13" max="16" width="13.85546875" style="26" customWidth="1"/>
-    <col min="17" max="18" width="12.7109375" style="26" customWidth="1"/>
-    <col min="19" max="20" width="12.28515625" style="26" customWidth="1"/>
-    <col min="21" max="23" width="13.140625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" style="26" customWidth="1"/>
-    <col min="25" max="27" width="15.28515625" style="26" customWidth="1"/>
-    <col min="28" max="30" width="10.85546875" style="26" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="26" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" style="25" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" style="25" customWidth="1"/>
+    <col min="13" max="16" width="13.88671875" style="26" customWidth="1"/>
+    <col min="17" max="18" width="12.6640625" style="26" customWidth="1"/>
+    <col min="19" max="20" width="12.33203125" style="26" customWidth="1"/>
+    <col min="21" max="23" width="13.109375" style="29" customWidth="1"/>
+    <col min="24" max="24" width="9.6640625" style="26" customWidth="1"/>
+    <col min="25" max="27" width="15.33203125" style="26" customWidth="1"/>
+    <col min="28" max="30" width="10.88671875" style="26" customWidth="1"/>
+    <col min="31" max="31" width="12.33203125" style="26" customWidth="1"/>
     <col min="32" max="32" width="18" style="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" ht="14.45" customHeight="1">
+    <row r="1" spans="1:67" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1164,7 +1169,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:67" s="7" customFormat="1" ht="45.75" customHeight="1">
+    <row r="2" spans="1:67" s="7" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1178,121 +1183,121 @@
         <v>4</v>
       </c>
       <c r="E2" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="G2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="H2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="I2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="J2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="K2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="L2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="M2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="30" t="s">
+      <c r="N2" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="30" t="s">
+      <c r="O2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="30" t="s">
+      <c r="P2" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="30" t="s">
+      <c r="Q2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="30" t="s">
+      <c r="R2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="30" t="s">
+      <c r="S2" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="33" t="s">
+      <c r="T2" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="33" t="s">
+      <c r="U2" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="30" t="s">
+      <c r="V2" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="30" t="s">
+      <c r="W2" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="30" t="s">
+      <c r="X2" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="31" t="s">
+      <c r="Y2" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="Z2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="AA2" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB2" s="39" t="s">
+      <c r="AC2" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="39" t="s">
-        <v>28</v>
-      </c>
       <c r="AD2" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE2" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="AE2" s="38" t="s">
-        <v>30</v>
-      </c>
       <c r="AF2" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG2" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="47" t="s">
+      <c r="AH2" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="AH2" s="47" t="s">
+      <c r="AI2" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="AI2" s="52" t="s">
+      <c r="AJ2" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="AJ2" s="50" t="s">
+      <c r="AK2" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="AK2" s="50" t="s">
+      <c r="AL2" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM2" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO2" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="AL2" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM2" s="50" t="s">
-        <v>11</v>
-      </c>
-      <c r="AN2" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO2" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="AP2" s="51" t="s">
-        <v>38</v>
+      <c r="AP2" s="50" t="s">
+        <v>65</v>
       </c>
       <c r="AQ2" s="35" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="AR2"/>
       <c r="AS2"/>
@@ -1319,7 +1324,7 @@
       <c r="BN2"/>
       <c r="BO2" s="32"/>
     </row>
-    <row r="3" spans="1:67">
+    <row r="3" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>42005</v>
       </c>
@@ -1440,7 +1445,7 @@
       <c r="AN3" s="48">
         <v>1</v>
       </c>
-      <c r="AO3" s="49">
+      <c r="AO3" s="2">
         <v>419.9</v>
       </c>
       <c r="AP3">
@@ -1450,7 +1455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:67">
+    <row r="4" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>42036</v>
       </c>
@@ -1577,7 +1582,7 @@
       <c r="AN4" s="48">
         <v>0.99203640500568824</v>
       </c>
-      <c r="AO4" s="49">
+      <c r="AO4" s="2">
         <v>348.1</v>
       </c>
       <c r="AP4">
@@ -1589,7 +1594,7 @@
         <v>9.6061055203509535E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:67">
+    <row r="5" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>42064</v>
       </c>
@@ -1716,7 +1721,7 @@
       <c r="AN5" s="48">
         <v>0.98805460750853225</v>
       </c>
-      <c r="AO5" s="49">
+      <c r="AO5" s="2">
         <v>334.9</v>
       </c>
       <c r="AP5">
@@ -1728,7 +1733,7 @@
         <v>1.1148086467075196E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:67">
+    <row r="6" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>42095</v>
       </c>
@@ -1855,7 +1860,7 @@
       <c r="AN6" s="48">
         <v>0.97781569965870307</v>
       </c>
-      <c r="AO6" s="49">
+      <c r="AO6" s="2">
         <v>335</v>
       </c>
       <c r="AP6">
@@ -1867,7 +1872,7 @@
         <v>1.1590945499374264E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:67">
+    <row r="7" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>42125</v>
       </c>
@@ -1994,7 +1999,7 @@
       <c r="AN7" s="48">
         <v>0.97042093287827069</v>
       </c>
-      <c r="AO7" s="49">
+      <c r="AO7" s="2">
         <v>341.1</v>
       </c>
       <c r="AP7">
@@ -2006,7 +2011,7 @@
         <v>1.1798481520554818E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:67">
+    <row r="8" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>42156</v>
       </c>
@@ -2133,7 +2138,7 @@
       <c r="AN8" s="48">
         <v>0.98179749715585884</v>
       </c>
-      <c r="AO8" s="49">
+      <c r="AO8" s="2">
         <v>354.3</v>
       </c>
       <c r="AP8">
@@ -2145,7 +2150,7 @@
         <v>1.2035901841666233E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:67">
+    <row r="9" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>42186</v>
       </c>
@@ -2272,7 +2277,7 @@
       <c r="AN9" s="48">
         <v>0.97895335608646183</v>
       </c>
-      <c r="AO9" s="49">
+      <c r="AO9" s="2">
         <v>340.3</v>
       </c>
       <c r="AP9">
@@ -2284,7 +2289,7 @@
         <v>1.1129611405513263E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:67">
+    <row r="10" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>42217</v>
       </c>
@@ -2411,7 +2416,7 @@
       <c r="AN10" s="48">
         <v>0.97042093287827069</v>
       </c>
-      <c r="AO10" s="49">
+      <c r="AO10" s="2">
         <v>314.7</v>
       </c>
       <c r="AP10">
@@ -2423,7 +2428,7 @@
         <v>1.0715785165362576E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:67">
+    <row r="11" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>42248</v>
       </c>
@@ -2550,7 +2555,7 @@
       <c r="AN11" s="48">
         <v>0.98577929465301484</v>
       </c>
-      <c r="AO11" s="49">
+      <c r="AO11" s="2">
         <v>303</v>
       </c>
       <c r="AP11">
@@ -2562,7 +2567,7 @@
         <v>1.1156682908293171E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:67">
+    <row r="12" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>42278</v>
       </c>
@@ -2689,7 +2694,7 @@
       <c r="AN12" s="48">
         <v>1.0102389078498293</v>
       </c>
-      <c r="AO12" s="49">
+      <c r="AO12" s="2">
         <v>247.3</v>
       </c>
       <c r="AP12">
@@ -2701,7 +2706,7 @@
         <v>9.4573767921403967E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:67">
+    <row r="13" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>42309</v>
       </c>
@@ -2828,7 +2833,7 @@
       <c r="AN13" s="48">
         <v>1.0568828213879409</v>
       </c>
-      <c r="AO13" s="49">
+      <c r="AO13" s="2">
         <v>227.3</v>
       </c>
       <c r="AP13">
@@ -2840,7 +2845,7 @@
         <v>1.0650365781260322E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:67">
+    <row r="14" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>42339</v>
       </c>
@@ -2967,7 +2972,7 @@
       <c r="AN14" s="48">
         <v>1.046075085324232</v>
       </c>
-      <c r="AO14" s="49">
+      <c r="AO14" s="2">
         <v>227.9</v>
       </c>
       <c r="AP14">
@@ -2979,7 +2984,7 @@
         <v>1.1618072806929449E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:67">
+    <row r="15" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>42370</v>
       </c>
@@ -3106,7 +3111,7 @@
       <c r="AN15" s="48">
         <v>1.0386803185437996</v>
       </c>
-      <c r="AO15" s="49">
+      <c r="AO15" s="2">
         <v>243.1</v>
       </c>
       <c r="AP15">
@@ -3118,7 +3123,7 @@
         <v>1.2360323514053702E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:67">
+    <row r="16" spans="1:67" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>42401</v>
       </c>
@@ -3245,7 +3250,7 @@
       <c r="AN16" s="48">
         <v>1.0091012514220705</v>
       </c>
-      <c r="AO16" s="49">
+      <c r="AO16" s="2">
         <v>245.2</v>
       </c>
       <c r="AP16">
@@ -3257,7 +3262,7 @@
         <v>1.1687583086942366E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>42430</v>
       </c>
@@ -3384,7 +3389,7 @@
       <c r="AN17" s="48">
         <v>1.0381114903299202</v>
       </c>
-      <c r="AO17" s="49">
+      <c r="AO17" s="2">
         <v>264.89999999999998</v>
       </c>
       <c r="AP17">
@@ -3396,7 +3401,7 @@
         <v>1.2518453968572018E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:43">
+    <row r="18" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>42461</v>
       </c>
@@ -3523,7 +3528,7 @@
       <c r="AN18" s="48">
         <v>1.0551763367463025</v>
       </c>
-      <c r="AO18" s="49">
+      <c r="AO18" s="2">
         <v>312.5</v>
       </c>
       <c r="AP18">
@@ -3535,7 +3540,7 @@
         <v>1.366964599335021E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:43">
+    <row r="19" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>42491</v>
       </c>
@@ -3662,7 +3667,7 @@
       <c r="AN19" s="48">
         <v>1.0813424345847553</v>
       </c>
-      <c r="AO19" s="49">
+      <c r="AO19" s="2">
         <v>344.1</v>
       </c>
       <c r="AP19">
@@ -3674,7 +3679,7 @@
         <v>1.2759212050984937E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:43">
+    <row r="20" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>42522</v>
       </c>
@@ -3801,7 +3806,7 @@
       <c r="AN20" s="48">
         <v>1.0853242320819112</v>
       </c>
-      <c r="AO20" s="49">
+      <c r="AO20" s="2">
         <v>329.6</v>
       </c>
       <c r="AP20">
@@ -3813,7 +3818,7 @@
         <v>1.1099201470374796E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:43">
+    <row r="21" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>42552</v>
       </c>
@@ -3940,7 +3945,7 @@
       <c r="AN21" s="48">
         <v>1.0784982935153582</v>
       </c>
-      <c r="AO21" s="49">
+      <c r="AO21" s="2">
         <v>318.39999999999998</v>
       </c>
       <c r="AP21">
@@ -3952,7 +3957,7 @@
         <v>1.1193736007829989E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:43">
+    <row r="22" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>42583</v>
       </c>
@@ -4079,7 +4084,7 @@
       <c r="AN22" s="48">
         <v>1.1126279863481228</v>
       </c>
-      <c r="AO22" s="49">
+      <c r="AO22" s="2">
         <v>314.8</v>
       </c>
       <c r="AP22">
@@ -4091,7 +4096,7 @@
         <v>1.145647123217478E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>42614</v>
       </c>
@@ -4218,7 +4223,7 @@
       <c r="AN23" s="48">
         <v>1.10580204778157</v>
       </c>
-      <c r="AO23" s="49">
+      <c r="AO23" s="2">
         <v>297</v>
       </c>
       <c r="AP23">
@@ -4230,7 +4235,7 @@
         <v>1.0932284619269384E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>42644</v>
       </c>
@@ -4357,7 +4362,7 @@
       <c r="AN24" s="48">
         <v>1.1131968145620021</v>
       </c>
-      <c r="AO24" s="49">
+      <c r="AO24" s="2">
         <v>278.5</v>
       </c>
       <c r="AP24">
@@ -4369,7 +4374,7 @@
         <v>1.0865706114837054E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:43">
+    <row r="25" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>42675</v>
       </c>
@@ -4496,7 +4501,7 @@
       <c r="AN25" s="48">
         <v>1.1069397042093287</v>
       </c>
-      <c r="AO25" s="49">
+      <c r="AO25" s="2">
         <v>305.3</v>
       </c>
       <c r="AP25">
@@ -4508,7 +4513,7 @@
         <v>1.270254695844108E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:43">
+    <row r="26" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>42705</v>
       </c>
@@ -4635,7 +4640,7 @@
       <c r="AN26" s="48">
         <v>1.1126279863481228</v>
       </c>
-      <c r="AO26" s="49">
+      <c r="AO26" s="2">
         <v>349.7</v>
       </c>
       <c r="AP26">
@@ -4647,7 +4652,7 @@
         <v>1.327266192211069E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:43">
+    <row r="27" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>42736</v>
       </c>
@@ -4774,7 +4779,7 @@
       <c r="AN27" s="48">
         <v>1.1336746302616609</v>
       </c>
-      <c r="AO27" s="49">
+      <c r="AO27" s="2">
         <v>384.9</v>
       </c>
       <c r="AP27">
@@ -4786,7 +4791,7 @@
         <v>1.2753855232974067E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:43">
+    <row r="28" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>42767</v>
       </c>
@@ -4913,7 +4918,7 @@
       <c r="AN28" s="48">
         <v>1.1427758816837315</v>
       </c>
-      <c r="AO28" s="49">
+      <c r="AO28" s="2">
         <v>379.9</v>
       </c>
       <c r="AP28">
@@ -4925,7 +4930,7 @@
         <v>1.1436959593122411E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:43">
+    <row r="29" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>42795</v>
       </c>
@@ -5057,7 +5062,7 @@
       <c r="AN29" s="48">
         <v>1.1683731513083049</v>
       </c>
-      <c r="AO29" s="49">
+      <c r="AO29" s="2">
         <v>408.3</v>
       </c>
       <c r="AP29">
@@ -5069,7 +5074,7 @@
         <v>1.2453725548926244E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:43">
+    <row r="30" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>42826</v>
       </c>
@@ -5201,7 +5206,7 @@
       <c r="AN30" s="48">
         <v>1.18259385665529</v>
       </c>
-      <c r="AO30" s="49">
+      <c r="AO30" s="2">
         <v>387</v>
       </c>
       <c r="AP30">
@@ -5213,7 +5218,7 @@
         <v>1.0982995088302428E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:43">
+    <row r="31" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>42856</v>
       </c>
@@ -5345,7 +5350,7 @@
       <c r="AN31" s="48">
         <v>1.204778156996587</v>
       </c>
-      <c r="AO31" s="49">
+      <c r="AO31" s="2">
         <v>383.3</v>
       </c>
       <c r="AP31">
@@ -5357,7 +5362,7 @@
         <v>1.1476700770403107E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:43">
+    <row r="32" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>42887</v>
       </c>
@@ -5489,7 +5494,7 @@
       <c r="AN32" s="48">
         <v>1.1672354948805459</v>
       </c>
-      <c r="AO32" s="49">
+      <c r="AO32" s="2">
         <v>378.7</v>
       </c>
       <c r="AP32">
@@ -5501,7 +5506,7 @@
         <v>1.1448423597114645E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:43">
+    <row r="33" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>42917</v>
       </c>
@@ -5633,7 +5638,7 @@
       <c r="AN33" s="48">
         <v>1.1717861205915812</v>
       </c>
-      <c r="AO33" s="49">
+      <c r="AO33" s="2">
         <v>380.8</v>
       </c>
       <c r="AP33">
@@ -5645,7 +5650,7 @@
         <v>1.1651741442716914E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:43">
+    <row r="34" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>42948</v>
       </c>
@@ -5777,7 +5782,7 @@
       <c r="AN34" s="48">
         <v>1.2098976109215016</v>
       </c>
-      <c r="AO34" s="49">
+      <c r="AO34" s="2">
         <v>400.2</v>
       </c>
       <c r="AP34">
@@ -5789,7 +5794,7 @@
         <v>1.2177814347059798E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:43">
+    <row r="35" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>42979</v>
       </c>
@@ -5921,7 +5926,7 @@
       <c r="AN35" s="48">
         <v>1.2098976109215016</v>
       </c>
-      <c r="AO35" s="49">
+      <c r="AO35" s="2">
         <v>408.8</v>
       </c>
       <c r="AP35">
@@ -5933,7 +5938,7 @@
         <v>1.1836491951011748E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:43">
+    <row r="36" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>43009</v>
       </c>
@@ -6065,7 +6070,7 @@
       <c r="AN36" s="48">
         <v>1.2935153583617747</v>
       </c>
-      <c r="AO36" s="49">
+      <c r="AO36" s="2">
         <v>388.9</v>
       </c>
       <c r="AP36">
@@ -6077,7 +6082,7 @@
         <v>1.1023417605268111E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:43">
+    <row r="37" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>43040</v>
       </c>
@@ -6209,7 +6214,7 @@
       <c r="AN37" s="48">
         <v>1.2468714448236631</v>
       </c>
-      <c r="AO37" s="49">
+      <c r="AO37" s="2">
         <v>379.3</v>
       </c>
       <c r="AP37">
@@ -6221,7 +6226,7 @@
         <v>1.1301448331405067E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:43">
+    <row r="38" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>43070</v>
       </c>
@@ -6353,7 +6358,7 @@
       <c r="AN38" s="48">
         <v>1.1427758816837315</v>
       </c>
-      <c r="AO38" s="49">
+      <c r="AO38" s="2">
         <v>400.4</v>
       </c>
       <c r="AP38">
@@ -6365,7 +6370,7 @@
         <v>1.2232083312585023E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:43">
+    <row r="39" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>43101</v>
       </c>
@@ -6497,7 +6502,7 @@
       <c r="AN39" s="48">
         <v>1.1467576791808873</v>
       </c>
-      <c r="AO39" s="49">
+      <c r="AO39" s="2">
         <v>440.5</v>
       </c>
       <c r="AP39">
@@ -6509,7 +6514,7 @@
         <v>1.2747970453648321E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:43">
+    <row r="40" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>43132</v>
       </c>
@@ -6641,7 +6646,7 @@
       <c r="AN40" s="48">
         <v>1.1916951080773606</v>
       </c>
-      <c r="AO40" s="49">
+      <c r="AO40" s="2">
         <v>450.9</v>
       </c>
       <c r="AP40">
@@ -6653,7 +6658,7 @@
         <v>1.1861060656080537E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:43">
+    <row r="41" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>43160</v>
       </c>
@@ -6785,7 +6790,7 @@
       <c r="AN41" s="48">
         <v>1.2445961319681456</v>
       </c>
-      <c r="AO41" s="49">
+      <c r="AO41" s="2">
         <v>471.6</v>
       </c>
       <c r="AP41">
@@ -6797,7 +6802,7 @@
         <v>1.2119445928536903E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:43">
+    <row r="42" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>43191</v>
       </c>
@@ -6929,7 +6934,7 @@
       <c r="AN42" s="48">
         <v>1.270193401592719</v>
       </c>
-      <c r="AO42" s="49">
+      <c r="AO42" s="2">
         <v>495.2</v>
       </c>
       <c r="AP42">
@@ -6941,7 +6946,7 @@
         <v>1.2167351203024736E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:43">
+    <row r="43" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>43221</v>
       </c>
@@ -7073,7 +7078,7 @@
       <c r="AN43" s="48">
         <v>1.2855517633674629</v>
       </c>
-      <c r="AO43" s="49">
+      <c r="AO43" s="2">
         <v>487.7</v>
       </c>
       <c r="AP43">
@@ -7085,7 +7090,7 @@
         <v>1.1411988461185667E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:43">
+    <row r="44" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>43252</v>
       </c>
@@ -7217,7 +7222,7 @@
       <c r="AN44" s="48">
         <v>1.3361774744027304</v>
       </c>
-      <c r="AO44" s="49">
+      <c r="AO44" s="2">
         <v>482.1</v>
       </c>
       <c r="AP44">
@@ -7229,7 +7234,7 @@
         <v>1.1454432575541401E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:43">
+    <row r="45" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>43282</v>
       </c>
@@ -7361,7 +7366,7 @@
       <c r="AN45" s="48">
         <v>1.2878270762229806</v>
       </c>
-      <c r="AO45" s="49">
+      <c r="AO45" s="2">
         <v>473.5</v>
       </c>
       <c r="AP45">
@@ -7373,7 +7378,7 @@
         <v>1.1380780733576042E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:43">
+    <row r="46" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>43313</v>
       </c>
@@ -7505,7 +7510,7 @@
       <c r="AN46" s="48">
         <v>1.1592718998862344</v>
       </c>
-      <c r="AO46" s="49">
+      <c r="AO46" s="2">
         <v>449.1</v>
       </c>
       <c r="AP46">
@@ -7517,7 +7522,7 @@
         <v>1.0990369049789481E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:43">
+    <row r="47" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>43344</v>
       </c>
@@ -7649,7 +7654,7 @@
       <c r="AN47" s="48">
         <v>1.1717861205915812</v>
       </c>
-      <c r="AO47" s="49">
+      <c r="AO47" s="2">
         <v>430.1</v>
       </c>
       <c r="AP47">
@@ -7661,7 +7666,7 @@
         <v>1.1097255667508573E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:43">
+    <row r="48" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>43374</v>
       </c>
@@ -7793,7 +7798,7 @@
       <c r="AN48" s="48">
         <v>1.1268486916951079</v>
       </c>
-      <c r="AO48" s="49">
+      <c r="AO48" s="2">
         <v>436.1</v>
       </c>
       <c r="AP48">
@@ -7805,7 +7810,7 @@
         <v>1.1749133767430734E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:43">
+    <row r="49" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>43405</v>
       </c>
@@ -7937,7 +7942,7 @@
       <c r="AN49" s="48">
         <v>1.0853242320819112</v>
       </c>
-      <c r="AO49" s="49">
+      <c r="AO49" s="2">
         <v>452.4</v>
       </c>
       <c r="AP49">
@@ -7949,7 +7954,7 @@
         <v>1.2020588046954692E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:43">
+    <row r="50" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>43435</v>
       </c>
@@ -8081,7 +8086,7 @@
       <c r="AN50" s="48">
         <v>1.064277588168373</v>
       </c>
-      <c r="AO50" s="49">
+      <c r="AO50" s="2">
         <v>453</v>
       </c>
       <c r="AP50">
@@ -8093,7 +8098,7 @@
         <v>1.1602853533568363E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:43">
+    <row r="51" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>43466</v>
       </c>
@@ -8225,7 +8230,7 @@
       <c r="AN51" s="48">
         <v>1.0574516496018203</v>
       </c>
-      <c r="AO51" s="49">
+      <c r="AO51" s="2">
         <v>417.9</v>
       </c>
       <c r="AP51">
@@ -8237,7 +8242,7 @@
         <v>1.0689647233967448E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:43">
+    <row r="52" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>43497</v>
       </c>
@@ -8369,7 +8374,7 @@
       <c r="AN52" s="48">
         <v>1.0858930602957906</v>
       </c>
-      <c r="AO52" s="49">
+      <c r="AO52" s="2">
         <v>410.7</v>
       </c>
       <c r="AP52">
@@ -8381,7 +8386,7 @@
         <v>1.138784470273899E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:43">
+    <row r="53" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43525</v>
       </c>
@@ -8513,7 +8518,7 @@
       <c r="AN53" s="48">
         <v>1.0955631399317405</v>
       </c>
-      <c r="AO53" s="49">
+      <c r="AO53" s="2">
         <v>433.9</v>
       </c>
       <c r="AP53">
@@ -8525,7 +8530,7 @@
         <v>1.2242050073624406E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:43">
+    <row r="54" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>43556</v>
       </c>
@@ -8657,7 +8662,7 @@
       <c r="AN54" s="48">
         <v>1.0944254835039817</v>
       </c>
-      <c r="AO54" s="49">
+      <c r="AO54" s="2">
         <v>416.6</v>
       </c>
       <c r="AP54">
@@ -8669,7 +8674,7 @@
         <v>1.1125481599024933E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:43">
+    <row r="55" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43586</v>
       </c>
@@ -8801,7 +8806,7 @@
       <c r="AN55" s="48">
         <v>1.0898748577929465</v>
       </c>
-      <c r="AO55" s="49">
+      <c r="AO55" s="2">
         <v>389.2</v>
       </c>
       <c r="AP55">
@@ -8813,7 +8818,7 @@
         <v>1.082537052973667E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:43">
+    <row r="56" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>43617</v>
       </c>
@@ -8945,7 +8950,7 @@
       <c r="AN56" s="48">
         <v>1.0540386803185438</v>
       </c>
-      <c r="AO56" s="49">
+      <c r="AO56" s="2">
         <v>350.3</v>
       </c>
       <c r="AP56">
@@ -8957,7 +8962,7 @@
         <v>1.0429332415544142E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:43">
+    <row r="57" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43647</v>
       </c>
@@ -9089,7 +9094,7 @@
       <c r="AN57" s="48">
         <v>1.0648464163822524</v>
       </c>
-      <c r="AO57" s="49">
+      <c r="AO57" s="2">
         <v>335.3</v>
       </c>
       <c r="AP57">
@@ -9101,7 +9106,7 @@
         <v>1.1091304291736036E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:43">
+    <row r="58" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>43678</v>
       </c>
@@ -9233,7 +9238,7 @@
       <c r="AN58" s="48">
         <v>1.0426621160409557</v>
       </c>
-      <c r="AO58" s="49">
+      <c r="AO58" s="2">
         <v>360.6</v>
       </c>
       <c r="AP58">
@@ -9245,7 +9250,7 @@
         <v>1.2461817109874453E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:43">
+    <row r="59" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43709</v>
       </c>
@@ -9377,7 +9382,7 @@
       <c r="AN59" s="48">
         <v>1.0540386803185438</v>
       </c>
-      <c r="AO59" s="49">
+      <c r="AO59" s="2">
         <v>320.39999999999998</v>
       </c>
       <c r="AP59">
@@ -9389,7 +9394,7 @@
         <v>1.0295702604581394E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:43">
+    <row r="60" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>43739</v>
       </c>
@@ -9524,7 +9529,7 @@
       <c r="AN60" s="48">
         <v>1.033560864618885</v>
       </c>
-      <c r="AO60" s="49">
+      <c r="AO60" s="2">
         <v>281.7</v>
       </c>
       <c r="AP60">
@@ -9536,7 +9541,7 @@
         <v>1.0187873501113181E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:43">
+    <row r="61" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43770</v>
       </c>
@@ -9671,7 +9676,7 @@
       <c r="AN61" s="48">
         <v>1.1052332195676906</v>
       </c>
-      <c r="AO61" s="49">
+      <c r="AO61" s="2">
         <v>299.10000000000002</v>
       </c>
       <c r="AP61">
@@ -9683,7 +9688,7 @@
         <v>1.2303219445256844E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:43">
+    <row r="62" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>43800</v>
       </c>
@@ -9818,7 +9823,7 @@
       <c r="AN62" s="48">
         <v>1.1086461888509669</v>
       </c>
-      <c r="AO62" s="49">
+      <c r="AO62" s="2">
         <v>334.9</v>
       </c>
       <c r="AP62">
@@ -9830,7 +9835,7 @@
         <v>1.297441958939778E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:43">
+    <row r="63" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43831</v>
       </c>
@@ -9965,7 +9970,7 @@
       <c r="AN63" s="48">
         <v>1.0790671217292376</v>
       </c>
-      <c r="AO63" s="49">
+      <c r="AO63" s="2">
         <v>376.4</v>
       </c>
       <c r="AP63">
@@ -9977,7 +9982,7 @@
         <v>1.3023378764073053E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:43">
+    <row r="64" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>43862</v>
       </c>
@@ -10112,7 +10117,7 @@
       <c r="AN64" s="48">
         <v>1.1473265073947667</v>
       </c>
-      <c r="AO64" s="49">
+      <c r="AO64" s="2">
         <v>349.3</v>
       </c>
       <c r="AP64">
@@ -10124,7 +10129,7 @@
         <v>1.0753211186541279E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:43">
+    <row r="65" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43891</v>
       </c>
@@ -10259,7 +10264,7 @@
       <c r="AN65" s="48">
         <v>1.2463026166097837</v>
       </c>
-      <c r="AO65" s="49">
+      <c r="AO65" s="2">
         <v>353.9</v>
       </c>
       <c r="AP65">
@@ -10271,7 +10276,7 @@
         <v>1.1740083378145132E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:43">
+    <row r="66" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>43922</v>
       </c>
@@ -10406,7 +10411,7 @@
       <c r="AN66" s="48">
         <v>1.110352673492605</v>
       </c>
-      <c r="AO66" s="49">
+      <c r="AO66" s="2">
         <v>310.39999999999998</v>
       </c>
       <c r="AP66">
@@ -10418,7 +10423,7 @@
         <v>1.0163197242315965E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:43">
+    <row r="67" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43952</v>
       </c>
@@ -10553,7 +10558,7 @@
       <c r="AN67" s="48">
         <v>1.1456200227531286</v>
       </c>
-      <c r="AO67" s="49">
+      <c r="AO67" s="2">
         <v>327.3</v>
       </c>
       <c r="AP67">
@@ -10565,7 +10570,7 @@
         <v>1.2218376318524449E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:43">
+    <row r="68" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>43983</v>
       </c>
@@ -10700,7 +10705,7 @@
       <c r="AN68" s="48">
         <v>1.2133105802047781</v>
       </c>
-      <c r="AO68" s="49">
+      <c r="AO68" s="2">
         <v>333.4</v>
       </c>
       <c r="AP68">
@@ -10712,7 +10717,7 @@
         <v>1.1803445374015922E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:43">
+    <row r="69" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>44013</v>
       </c>
@@ -10847,7 +10852,7 @@
       <c r="AN69" s="48">
         <v>1.2866894197952217</v>
       </c>
-      <c r="AO69" s="49">
+      <c r="AO69" s="2">
         <v>314.3</v>
       </c>
       <c r="AP69">
@@ -10859,7 +10864,7 @@
         <v>1.092365536162756E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:43">
+    <row r="70" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>44044</v>
       </c>
@@ -10994,7 +10999,7 @@
       <c r="AN70" s="48">
         <v>1.5682593856655289</v>
       </c>
-      <c r="AO70" s="49">
+      <c r="AO70" s="2">
         <v>330.1</v>
       </c>
       <c r="AP70">
@@ -11006,7 +11011,7 @@
         <v>1.2169993537110371E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:43">
+    <row r="71" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>44075</v>
       </c>
@@ -11141,7 +11146,7 @@
       <c r="AN71" s="48">
         <v>1.7332195676905573</v>
       </c>
-      <c r="AO71" s="49">
+      <c r="AO71" s="2">
         <v>370.3</v>
       </c>
       <c r="AP71">
@@ -11153,7 +11158,7 @@
         <v>1.2998624315185222E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:43">
+    <row r="72" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>44105</v>
       </c>
@@ -11288,7 +11293,7 @@
       <c r="AN72" s="48">
         <v>1.7821387940841866</v>
       </c>
-      <c r="AO72" s="49">
+      <c r="AO72" s="2">
         <v>371.5</v>
       </c>
       <c r="AP72">
@@ -11300,7 +11305,7 @@
         <v>1.1625036103325449E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:43">
+    <row r="73" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>44136</v>
       </c>
@@ -11435,7 +11440,7 @@
       <c r="AN73" s="48">
         <v>1.7525597269624573</v>
       </c>
-      <c r="AO73" s="49">
+      <c r="AO73" s="2">
         <v>377.5</v>
       </c>
       <c r="AP73">
@@ -11447,7 +11452,7 @@
         <v>1.177463198426722E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:43">
+    <row r="74" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>44166</v>
       </c>
@@ -11582,7 +11587,7 @@
       <c r="AN74" s="48">
         <v>1.7116040955631397</v>
       </c>
-      <c r="AO74" s="49">
+      <c r="AO74" s="2">
         <v>471.6</v>
       </c>
       <c r="AP74">
@@ -11594,7 +11599,7 @@
         <v>1.4475915679939839E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:43">
+    <row r="75" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>44197</v>
       </c>
@@ -11729,7 +11734,7 @@
       <c r="AN75" s="48">
         <v>1.8668941979522182</v>
       </c>
-      <c r="AO75" s="49">
+      <c r="AO75" s="2">
         <v>576.70000000000005</v>
       </c>
       <c r="AP75">
@@ -11741,7 +11746,7 @@
         <v>1.4169853470889268E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:43">
+    <row r="76" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>44228</v>
       </c>
@@ -11876,7 +11881,7 @@
       <c r="AN76" s="48">
         <v>1.9795221843003412</v>
       </c>
-      <c r="AO76" s="49">
+      <c r="AO76" s="2">
         <v>530.79999999999995</v>
       </c>
       <c r="AP76">
@@ -11888,7 +11893,7 @@
         <v>1.0665228561996462E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:43">
+    <row r="77" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>44256</v>
       </c>
@@ -12023,7 +12028,7 @@
       <c r="AN77" s="48">
         <v>2.0961319681456199</v>
       </c>
-      <c r="AO77" s="49">
+      <c r="AO77" s="2">
         <v>574.20000000000005</v>
       </c>
       <c r="AP77">
@@ -12035,7 +12040,7 @@
         <v>1.253491745117233E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:43">
+    <row r="78" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>44287</v>
       </c>
@@ -12170,7 +12175,7 @@
       <c r="AN78" s="48">
         <v>2.3230944254835038</v>
       </c>
-      <c r="AO78" s="49">
+      <c r="AO78" s="2">
         <v>554.5</v>
       </c>
       <c r="AP78">
@@ -12182,7 +12187,7 @@
         <v>1.1189935072142288E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:43">
+    <row r="79" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>44317</v>
       </c>
@@ -12317,7 +12322,7 @@
       <c r="AN79" s="48">
         <v>2.6052332195676904</v>
       </c>
-      <c r="AO79" s="49">
+      <c r="AO79" s="2">
         <v>577.1</v>
       </c>
       <c r="AP79">
@@ -12329,7 +12334,7 @@
         <v>1.2059761751267153E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:43">
+    <row r="80" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>44348</v>
       </c>
@@ -12464,7 +12469,7 @@
       <c r="AN80" s="48">
         <v>2.8617747440273038</v>
       </c>
-      <c r="AO80" s="49">
+      <c r="AO80" s="2">
         <v>635.9</v>
       </c>
       <c r="AP80">
@@ -12476,7 +12481,7 @@
         <v>1.2768119978162278E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:43">
+    <row r="81" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>44378</v>
       </c>
@@ -12611,7 +12616,7 @@
       <c r="AN81" s="48">
         <v>2.8785836177474402</v>
       </c>
-      <c r="AO81" s="49">
+      <c r="AO81" s="2">
         <v>648.06100000000004</v>
       </c>
       <c r="AP81">
@@ -12623,7 +12628,7 @@
         <v>1.1809085470597872E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:43">
+    <row r="82" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>44409</v>
       </c>
@@ -12758,7 +12763,7 @@
       <c r="AN82" s="48">
         <v>2.0014562002275311</v>
       </c>
-      <c r="AO82" s="49">
+      <c r="AO82" s="2">
         <v>636.86599999999999</v>
       </c>
       <c r="AP82">
@@ -12770,7 +12775,7 @@
         <v>1.1387316240918002E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:43">
+    <row r="83" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>44440</v>
       </c>
@@ -12905,7 +12910,7 @@
       <c r="AN83" s="48">
         <v>1.8854721274175199</v>
       </c>
-      <c r="AO83" s="49">
+      <c r="AO83" s="2">
         <v>608.08100000000002</v>
       </c>
       <c r="AP83">
@@ -12917,7 +12922,7 @@
         <v>1.106375560924555E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:43">
+    <row r="84" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>44470</v>
       </c>
@@ -13052,7 +13057,7 @@
       <c r="AN84" s="48">
         <v>1.9418543799772467</v>
       </c>
-      <c r="AO84" s="49">
+      <c r="AO84" s="2">
         <v>605.35199999999998</v>
       </c>
       <c r="AP84">
@@ -13064,7 +13069,7 @@
         <v>1.1535482167450694E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:43">
+    <row r="85" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>44501</v>
       </c>
@@ -13199,7 +13204,7 @@
       <c r="AN85" s="48">
         <v>1.9904664391353808</v>
       </c>
-      <c r="AO85" s="49">
+      <c r="AO85" s="2">
         <v>659.61300000000006</v>
       </c>
       <c r="AP85">
@@ -13211,7 +13216,7 @@
         <v>1.2626135014718539E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:43">
+    <row r="86" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>44531</v>
       </c>
@@ -13346,7 +13351,7 @@
       <c r="AN86" s="48">
         <v>2.052172923777019</v>
       </c>
-      <c r="AO86" s="49">
+      <c r="AO86" s="2">
         <v>647.12400000000002</v>
       </c>
       <c r="AP86">
@@ -13358,7 +13363,7 @@
         <v>1.1368090041926142E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:43">
+    <row r="87" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>44562</v>
       </c>
@@ -13493,7 +13498,7 @@
       <c r="AN87" s="48">
         <v>2.3435893060295787</v>
       </c>
-      <c r="AO87" s="49">
+      <c r="AO87" s="2">
         <v>603.16300000000001</v>
       </c>
       <c r="AP87">
@@ -13505,7 +13510,7 @@
         <v>1.0800314199553475E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:43">
+    <row r="88" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>44593</v>
       </c>
@@ -13640,7 +13645,7 @@
       <c r="AN88" s="48">
         <v>2.7702901023890782</v>
       </c>
-      <c r="AO88" s="49">
+      <c r="AO88" s="2">
         <v>602.69399999999996</v>
       </c>
       <c r="AP88">
@@ -13652,7 +13657,7 @@
         <v>1.1578475462462063E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:43">
+    <row r="89" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>44621</v>
       </c>
@@ -13787,7 +13792,7 @@
       <c r="AN89" s="48">
         <v>3.1543856655290101</v>
       </c>
-      <c r="AO89" s="49">
+      <c r="AO89" s="2">
         <v>754.73</v>
       </c>
       <c r="AP89">
@@ -13799,7 +13804,7 @@
         <v>1.4510552524533715E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:43">
+    <row r="90" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>44652</v>
       </c>
@@ -13934,7 +13939,7 @@
       <c r="AN90" s="48">
         <v>2.7985494880546073</v>
       </c>
-      <c r="AO90" s="49">
+      <c r="AO90" s="2">
         <v>754.63699999999994</v>
       </c>
       <c r="AP90">
@@ -13946,7 +13951,7 @@
         <v>1.1586057672370736E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:43">
+    <row r="91" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>44682</v>
       </c>
@@ -14081,7 +14086,7 @@
       <c r="AN91" s="48">
         <v>2.4457167235494879</v>
       </c>
-      <c r="AO91" s="49">
+      <c r="AO91" s="2">
         <v>663.66800000000001</v>
       </c>
       <c r="AP91">
@@ -14093,7 +14098,7 @@
         <v>1.0190652376170039E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:43">
+    <row r="92" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>44713</v>
       </c>
@@ -14228,7 +14233,7 @@
       <c r="AN92" s="48">
         <v>2.1469738339021611</v>
       </c>
-      <c r="AO92" s="49">
+      <c r="AO92" s="2">
         <v>594.81799999999998</v>
       </c>
       <c r="AP92">
@@ -14240,7 +14245,7 @@
         <v>1.0385380882374623E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:43">
+    <row r="93" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>44743</v>
       </c>
@@ -14375,7 +14380,7 @@
       <c r="AN93" s="48">
         <v>1.8869624573378838</v>
       </c>
-      <c r="AO93" s="49">
+      <c r="AO93" s="2">
         <v>516.83799999999997</v>
       </c>
       <c r="AP93">
@@ -14387,7 +14392,7 @@
         <v>1.0068378628309754E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:43">
+    <row r="94" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>44774</v>
       </c>
@@ -14522,7 +14527,7 @@
       <c r="AN94" s="48">
         <v>1.9943742889647325</v>
       </c>
-      <c r="AO94" s="49">
+      <c r="AO94" s="2">
         <v>475.38099999999997</v>
       </c>
       <c r="AP94">
@@ -14534,7 +14539,7 @@
         <v>1.0658021375966812E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:43">
+    <row r="95" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>44805</v>
       </c>
@@ -14669,7 +14674,7 @@
       <c r="AN95" s="48">
         <v>1.8626450511945389</v>
       </c>
-      <c r="AO95" s="49">
+      <c r="AO95" s="2">
         <v>460.541</v>
       </c>
       <c r="AP95">
@@ -14681,7 +14686,7 @@
         <v>1.1225758216798299E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:43">
+    <row r="96" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>44835</v>
       </c>
@@ -14816,7 +14821,7 @@
       <c r="AN96" s="48">
         <v>1.8117349260523321</v>
       </c>
-      <c r="AO96" s="49">
+      <c r="AO96" s="2">
         <v>445.00599999999997</v>
       </c>
       <c r="AP96">
@@ -14828,7 +14833,7 @@
         <v>1.1196615674552919E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:43">
+    <row r="97" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>44866</v>
       </c>
@@ -14963,7 +14968,7 @@
       <c r="AN97" s="48">
         <v>1.8060580204778156</v>
       </c>
-      <c r="AO97" s="49">
+      <c r="AO97" s="2">
         <v>430.14800000000002</v>
       </c>
       <c r="AP97">
@@ -14975,7 +14980,7 @@
         <v>1.1200598912335678E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:43">
+    <row r="98" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>44896</v>
       </c>
@@ -15110,7 +15115,7 @@
       <c r="AN98" s="48">
         <v>1.6552389078498291</v>
       </c>
-      <c r="AO98" s="49">
+      <c r="AO98" s="2">
         <v>452.44200000000001</v>
       </c>
       <c r="AP98">
@@ -15122,7 +15127,7 @@
         <v>1.2188049512420371E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:43">
+    <row r="99" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>44927</v>
       </c>
@@ -15257,7 +15262,7 @@
       <c r="AN99" s="48">
         <v>1.5549317406143346</v>
       </c>
-      <c r="AO99" s="49">
+      <c r="AO99" s="2">
         <v>500.68799999999999</v>
       </c>
       <c r="AP99">
@@ -15269,7 +15274,7 @@
         <v>1.2823113123574547E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:43">
+    <row r="100" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>44958</v>
       </c>
@@ -15376,7 +15381,7 @@
       <c r="AN100" s="48">
         <v>1.543202502844141</v>
       </c>
-      <c r="AO100" s="49">
+      <c r="AO100" s="2">
         <v>530.59199999999998</v>
       </c>
       <c r="AP100">
@@ -15388,7 +15393,7 @@
         <v>1.2279557558232086E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:43">
+    <row r="101" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>44986</v>
       </c>
@@ -15495,7 +15500,7 @@
       <c r="AN101" s="48">
         <v>1.5548065984072807</v>
       </c>
-      <c r="AO101" s="49">
+      <c r="AO101" s="2">
         <v>582.35400000000004</v>
       </c>
       <c r="AP101">
@@ -15507,7 +15512,7 @@
         <v>1.2717904793093046E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:43">
+    <row r="102" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>45017</v>
       </c>
@@ -15614,7 +15619,7 @@
       <c r="AN102" s="48">
         <v>1.5872127417519908</v>
       </c>
-      <c r="AO102" s="49">
+      <c r="AO102" s="2">
         <v>569.41300000000001</v>
       </c>
       <c r="AP102">
@@ -15626,7 +15631,7 @@
         <v>1.1329989817050948E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:43">
+    <row r="103" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>45047</v>
       </c>
@@ -15733,7 +15738,7 @@
       <c r="AN103" s="48">
         <v>1.6839021615472125</v>
       </c>
-      <c r="AO103" s="49">
+      <c r="AO103" s="2">
         <v>539.423</v>
       </c>
       <c r="AP103">
@@ -15745,7 +15750,7 @@
         <v>1.0977192651563541E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:43">
+    <row r="104" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>45078</v>
       </c>
@@ -15852,7 +15857,7 @@
       <c r="AN104" s="48">
         <v>1.7311888509670079</v>
       </c>
-      <c r="AO104" s="49">
+      <c r="AO104" s="2">
         <v>485.84399999999999</v>
       </c>
       <c r="AP104">
@@ -15864,7 +15869,7 @@
         <v>1.0436541105703889E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:43">
+    <row r="105" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>45108</v>
       </c>
@@ -15971,7 +15976,7 @@
       <c r="AN105" s="48">
         <v>1.8436177474402728</v>
       </c>
-      <c r="AO105" s="49">
+      <c r="AO105" s="2">
         <v>471.10899999999998</v>
       </c>
       <c r="AP105">
@@ -15983,7 +15988,7 @@
         <v>1.1236052547297298E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:43">
+    <row r="106" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>45139</v>
       </c>
@@ -16090,7 +16095,7 @@
       <c r="AN106" s="48">
         <v>2.0919112627986345</v>
       </c>
-      <c r="AO106" s="49">
+      <c r="AO106" s="2">
         <v>475.411</v>
       </c>
       <c r="AP106">
@@ -16102,7 +16107,7 @@
         <v>1.1693298316265248E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:43">
+    <row r="107" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>45170</v>
       </c>
@@ -16209,7 +16214,7 @@
       <c r="AN107" s="48">
         <v>2.0887030716723549</v>
       </c>
-      <c r="AO107" s="49">
+      <c r="AO107" s="2">
         <v>478.80200000000002</v>
       </c>
       <c r="AP107">
@@ -16221,7 +16226,7 @@
         <v>1.1670136450063104E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:43">
+    <row r="108" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>45200</v>
       </c>
@@ -16328,7 +16333,7 @@
       <c r="AN108" s="48">
         <v>1.7051023890784982</v>
       </c>
-      <c r="AO108" s="49">
+      <c r="AO108" s="2">
         <v>468.226</v>
       </c>
       <c r="AP108">
@@ -16340,7 +16345,7 @@
         <v>1.1331535776892136E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:43">
+    <row r="109" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>45231</v>
       </c>
@@ -16447,7 +16452,7 @@
       <c r="AN109" s="48">
         <v>1.664334470989761</v>
       </c>
-      <c r="AO109" s="49">
+      <c r="AO109" s="2">
         <v>486.22399999999999</v>
       </c>
       <c r="AP109">
@@ -16459,7 +16464,7 @@
         <v>1.2032893426161838E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:43">
+    <row r="110" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>45261</v>
       </c>
@@ -16566,7 +16571,7 @@
       <c r="AN110" s="48">
         <v>1.7144311717861205</v>
       </c>
-      <c r="AO110" s="49">
+      <c r="AO110" s="2">
         <v>533.73800000000006</v>
       </c>
       <c r="AP110">
@@ -16578,7 +16583,7 @@
         <v>1.2719819145390438E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:43">
+    <row r="111" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>45292</v>
       </c>
@@ -16685,7 +16690,7 @@
       <c r="AN111" s="48">
         <v>1.7166382252559726</v>
       </c>
-      <c r="AO111" s="49">
+      <c r="AO111" s="2">
         <v>542.15499999999997</v>
       </c>
       <c r="AP111">
@@ -16697,7 +16702,7 @@
         <v>1.1770219114497164E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:43">
+    <row r="112" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>45323</v>
       </c>
@@ -16804,7 +16809,7 @@
       <c r="AN112" s="48">
         <v>1.7085324232081911</v>
       </c>
-      <c r="AO112" s="49">
+      <c r="AO112" s="2">
         <v>526.53399999999999</v>
       </c>
       <c r="AP112">
@@ -16816,7 +16821,7 @@
         <v>1.125361768957886E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:43">
+    <row r="113" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>45352</v>
       </c>
@@ -16923,7 +16928,7 @@
       <c r="AN113" s="48">
         <v>1.8278498293515357</v>
       </c>
-      <c r="AO113" s="49">
+      <c r="AO113" s="2">
         <v>485.7</v>
       </c>
       <c r="AP113">
@@ -16935,7 +16940,7 @@
         <v>1.0688847662160196E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:43">
+    <row r="114" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>45383</v>
       </c>
@@ -17042,7 +17047,7 @@
       <c r="AN114" s="48">
         <v>2.1502844141069395</v>
       </c>
-      <c r="AO114" s="49">
+      <c r="AO114" s="2">
         <v>476.41699999999997</v>
       </c>
       <c r="AP114">
@@ -17054,7 +17059,7 @@
         <v>1.1366018297109618E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:43">
+    <row r="115" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>45413</v>
       </c>
@@ -17161,7 +17166,7 @@
       <c r="AN115" s="48">
         <v>1.8725028441410692</v>
       </c>
-      <c r="AO115" s="49">
+      <c r="AO115" s="2">
         <v>474.86799999999999</v>
       </c>
       <c r="AP115">
@@ -17173,7 +17178,7 @@
         <v>1.1549810506011353E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:43">
+    <row r="116" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>45444</v>
       </c>
@@ -17280,7 +17285,7 @@
       <c r="AN116" s="48">
         <v>1.7864903299203638</v>
       </c>
-      <c r="AO116" s="49">
+      <c r="AO116" s="2">
         <v>457.471</v>
       </c>
       <c r="AP116">
@@ -17292,7 +17297,7 @@
         <v>1.1162972839455949E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:43">
+    <row r="117" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>45474</v>
       </c>
@@ -17399,7 +17404,7 @@
       <c r="AN117" s="48">
         <v>1.5501877133105801</v>
       </c>
-      <c r="AO117" s="49">
+      <c r="AO117" s="2">
         <v>459.48500000000001</v>
       </c>
       <c r="AP117">
@@ -17411,7 +17416,7 @@
         <v>1.1638499013391607E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:43">
+    <row r="118" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>45505</v>
       </c>
@@ -17518,7 +17523,7 @@
       <c r="AN118" s="48">
         <v>1.5291240045506256</v>
       </c>
-      <c r="AO118" s="49">
+      <c r="AO118" s="2">
         <v>457.12900000000002</v>
       </c>
       <c r="AP118">
@@ -17530,7 +17535,7 @@
         <v>1.152807091913864E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:43">
+    <row r="119" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>45536</v>
       </c>
@@ -17637,7 +17642,7 @@
       <c r="AN119" s="48">
         <v>1.5210693970420932</v>
       </c>
-      <c r="AO119" s="49">
+      <c r="AO119" s="2">
         <v>453.32499999999999</v>
       </c>
       <c r="AP119">
@@ -17649,7 +17654,7 @@
         <v>1.1491060228904556E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:43">
+    <row r="120" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>45566</v>
       </c>
@@ -17756,7 +17761,7 @@
       <c r="AN120" s="48">
         <v>1.5162969283276448</v>
       </c>
-      <c r="AO120" s="49">
+      <c r="AO120" s="2">
         <v>462.25</v>
       </c>
       <c r="AP120">
@@ -17768,7 +17773,7 @@
         <v>1.1815618330350247E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:43">
+    <row r="121" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>45597</v>
       </c>
@@ -17875,7 +17880,7 @@
       <c r="AN121" s="48">
         <v>1.6133503981797497</v>
       </c>
-      <c r="AO121" s="49">
+      <c r="AO121" s="2">
         <v>463.74200000000002</v>
       </c>
       <c r="AP121">
@@ -17887,7 +17892,7 @@
         <v>1.1624886334224694E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:43">
+    <row r="122" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>45627</v>
       </c>
@@ -17994,7 +17999,7 @@
       <c r="AN122" s="48">
         <v>1.6847383390216155</v>
       </c>
-      <c r="AO122" s="49">
+      <c r="AO122" s="2">
         <v>451.71600000000001</v>
       </c>
       <c r="AP122">
@@ -18006,7 +18011,7 @@
         <v>1.1286992783022113E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:43">
+    <row r="123" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>45658</v>
       </c>
@@ -18113,7 +18118,7 @@
       <c r="AN123" s="48">
         <v>1.615022753128555</v>
       </c>
-      <c r="AO123" s="49">
+      <c r="AO123" s="2">
         <v>465.87400000000002</v>
       </c>
       <c r="AP123">
@@ -18125,7 +18130,7 @@
         <v>1.1950668621688663E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:43">
+    <row r="124" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>45689</v>
       </c>
@@ -18232,7 +18237,7 @@
       <c r="AN124" s="48">
         <v>1.6104323094425481</v>
       </c>
-      <c r="AO124" s="49">
+      <c r="AO124" s="2">
         <v>503.82299999999998</v>
       </c>
       <c r="AP124">
@@ -18244,7 +18249,7 @@
         <v>1.2531374824411443E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:43">
+    <row r="125" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>45717</v>
       </c>
@@ -18351,7 +18356,7 @@
       <c r="AN125" s="48">
         <v>1.6240955631399316</v>
       </c>
-      <c r="AO125" s="49">
+      <c r="AO125" s="2">
         <v>532.28300000000002</v>
       </c>
       <c r="AP125">
@@ -18363,7 +18368,7 @@
         <v>1.2242040464057934E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:43">
+    <row r="126" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>45748</v>
       </c>
@@ -18470,7 +18475,7 @@
       <c r="AN126" s="48">
         <v>1.551655290102389</v>
       </c>
-      <c r="AO126" s="49">
+      <c r="AO126" s="2">
         <v>495.81200000000001</v>
       </c>
       <c r="AP126">
@@ -18482,7 +18487,7 @@
         <v>1.0793533455853445E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:43">
+    <row r="127" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>45778</v>
       </c>
@@ -18589,7 +18594,7 @@
       <c r="AN127" s="48">
         <v>1.4905858930602958</v>
       </c>
-      <c r="AO127" s="49">
+      <c r="AO127" s="2">
         <v>470.95400000000001</v>
       </c>
       <c r="AP127">
@@ -18601,7 +18606,7 @@
         <v>1.1006536053048702E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:43">
+    <row r="128" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>45809</v>
       </c>
@@ -18708,7 +18713,7 @@
       <c r="AN128" s="48">
         <v>1.376626848691695</v>
       </c>
-      <c r="AO128" s="49">
+      <c r="AO128" s="2">
         <v>465.96499999999997</v>
       </c>
       <c r="AP128">
@@ -18720,7 +18725,7 @@
         <v>1.1464734747547828E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:43">
+    <row r="129" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>45839</v>
       </c>
@@ -18825,7 +18830,7 @@
       <c r="AN129" s="48">
         <v>1.340688282138794</v>
       </c>
-      <c r="AO129" s="49">
+      <c r="AO129" s="2">
         <v>463.37400000000002</v>
       </c>
       <c r="AP129">
@@ -18837,7 +18842,7 @@
         <v>1.1523053262209842E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:43">
+    <row r="130" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>45870</v>
       </c>
@@ -18939,7 +18944,7 @@
       <c r="AN130" s="48">
         <v>1.2782195676905574</v>
       </c>
-      <c r="AO130" s="49">
+      <c r="AO130" s="2">
         <v>464.87799999999999</v>
       </c>
       <c r="AP130">
@@ -18948,7 +18953,7 @@
       </c>
       <c r="AQ130" s="27"/>
     </row>
-    <row r="131" spans="1:43">
+    <row r="131" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>45901</v>
       </c>
@@ -19047,7 +19052,7 @@
       <c r="AN131" s="48">
         <v>1.2620307167235494</v>
       </c>
-      <c r="AO131" s="49">
+      <c r="AO131" s="2">
         <v>461.75099999999998</v>
       </c>
       <c r="AP131">
@@ -19056,7 +19061,7 @@
       </c>
       <c r="AQ131" s="27"/>
     </row>
-    <row r="132" spans="1:43">
+    <row r="132" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>45931</v>
       </c>
@@ -19155,7 +19160,7 @@
       <c r="AN132" s="48">
         <v>1.2586120591581342</v>
       </c>
-      <c r="AO132" s="49">
+      <c r="AO132" s="2">
         <v>453.80900000000003</v>
       </c>
       <c r="AP132">
@@ -19164,7 +19169,7 @@
       </c>
       <c r="AQ132" s="27"/>
     </row>
-    <row r="133" spans="1:43">
+    <row r="133" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>45962</v>
       </c>
@@ -19263,7 +19268,7 @@
       <c r="AN133" s="48">
         <v>1.2558248009101252</v>
       </c>
-      <c r="AO133" s="49">
+      <c r="AO133" s="2">
         <v>451.39600000000002</v>
       </c>
       <c r="AP133">
@@ -19272,7 +19277,7 @@
       </c>
       <c r="AQ133" s="27"/>
     </row>
-    <row r="134" spans="1:43">
+    <row r="134" spans="1:43" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>45992</v>
       </c>
@@ -19371,7 +19376,7 @@
       <c r="AN134" s="48">
         <v>1.2238794084186575</v>
       </c>
-      <c r="AO134" s="49">
+      <c r="AO134" s="2">
         <v>470.11</v>
       </c>
       <c r="AP134">
@@ -19380,13 +19385,13 @@
       </c>
       <c r="AQ134" s="27"/>
     </row>
-    <row r="135" spans="1:43" ht="15" customHeight="1">
+    <row r="135" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AQ135" s="26"/>
     </row>
-    <row r="136" spans="1:43" ht="15" customHeight="1">
+    <row r="136" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AQ136" s="26"/>
     </row>
-    <row r="137" spans="1:43" ht="15" customHeight="1">
+    <row r="137" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AQ137" s="26"/>
     </row>
   </sheetData>
@@ -19399,30 +19404,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A64A41-F43F-4361-AE33-6FD373C824AF}">
   <dimension ref="A1:BS136"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="9.140625" style="24"/>
-    <col min="6" max="9" width="13.85546875" style="25" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="25" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" style="25" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="25" customWidth="1"/>
-    <col min="13" max="15" width="13.85546875" style="26" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="26" customWidth="1"/>
-    <col min="17" max="17" width="13.28515625" style="26" customWidth="1"/>
-    <col min="18" max="18" width="12.28515625" style="26" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" style="29" customWidth="1"/>
-    <col min="20" max="20" width="12.140625" style="26" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" style="26" customWidth="1"/>
-    <col min="22" max="23" width="10.85546875" style="26" customWidth="1"/>
-    <col min="24" max="24" width="12.28515625" style="26" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="9.109375" style="24"/>
+    <col min="6" max="9" width="13.88671875" style="25" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" style="25" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" style="25" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" style="25" customWidth="1"/>
+    <col min="13" max="15" width="13.88671875" style="26" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" style="26" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="26" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" style="26" customWidth="1"/>
+    <col min="19" max="19" width="13.109375" style="29" customWidth="1"/>
+    <col min="20" max="20" width="12.109375" style="26" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" style="26" customWidth="1"/>
+    <col min="22" max="23" width="10.88671875" style="26" customWidth="1"/>
+    <col min="24" max="24" width="12.33203125" style="26" customWidth="1"/>
     <col min="25" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" ht="14.45" customHeight="1">
+    <row r="1" spans="1:71" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B1" s="18">
         <v>1</v>
@@ -19471,78 +19476,78 @@
       <c r="X1" s="20"/>
       <c r="Y1" s="17"/>
     </row>
-    <row r="2" spans="1:71" s="7" customFormat="1" ht="45.75" customHeight="1">
+    <row r="2" spans="1:71" s="7" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="Q2" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="30" t="s">
+      <c r="R2" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="S2" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q2" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="R2" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="S2" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="T2" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="30" t="s">
-        <v>48</v>
-      </c>
       <c r="V2" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="W2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="W2" s="34" t="s">
-        <v>29</v>
-      </c>
       <c r="X2" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Y2" s="4"/>
       <c r="Z2"/>
@@ -19592,7 +19597,7 @@
       <c r="BR2"/>
       <c r="BS2" s="32"/>
     </row>
-    <row r="3" spans="1:71" ht="14.45">
+    <row r="3" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>42005</v>
       </c>
@@ -19670,7 +19675,7 @@
       </c>
       <c r="Y3" s="3"/>
     </row>
-    <row r="4" spans="1:71" ht="14.45">
+    <row r="4" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>42036</v>
       </c>
@@ -19749,7 +19754,7 @@
       </c>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:71" ht="14.45">
+    <row r="5" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>42064</v>
       </c>
@@ -19828,7 +19833,7 @@
       </c>
       <c r="Y5" s="3"/>
     </row>
-    <row r="6" spans="1:71" ht="14.45">
+    <row r="6" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>42095</v>
       </c>
@@ -19907,7 +19912,7 @@
       </c>
       <c r="Y6" s="3"/>
     </row>
-    <row r="7" spans="1:71" ht="14.45">
+    <row r="7" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>42125</v>
       </c>
@@ -19986,7 +19991,7 @@
       </c>
       <c r="Y7" s="3"/>
     </row>
-    <row r="8" spans="1:71" ht="14.45">
+    <row r="8" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>42156</v>
       </c>
@@ -20065,7 +20070,7 @@
       </c>
       <c r="Y8" s="3"/>
     </row>
-    <row r="9" spans="1:71" ht="14.45">
+    <row r="9" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>42186</v>
       </c>
@@ -20144,7 +20149,7 @@
       </c>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" spans="1:71" ht="14.45">
+    <row r="10" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>42217</v>
       </c>
@@ -20223,7 +20228,7 @@
       </c>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" spans="1:71" ht="14.45">
+    <row r="11" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>42248</v>
       </c>
@@ -20302,7 +20307,7 @@
       </c>
       <c r="Y11" s="3"/>
     </row>
-    <row r="12" spans="1:71" ht="14.45">
+    <row r="12" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>42278</v>
       </c>
@@ -20381,7 +20386,7 @@
       </c>
       <c r="Y12" s="3"/>
     </row>
-    <row r="13" spans="1:71" ht="14.45">
+    <row r="13" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>42309</v>
       </c>
@@ -20460,7 +20465,7 @@
       </c>
       <c r="Y13" s="3"/>
     </row>
-    <row r="14" spans="1:71" ht="14.45">
+    <row r="14" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>42339</v>
       </c>
@@ -20539,7 +20544,7 @@
       </c>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:71" ht="14.45">
+    <row r="15" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>42370</v>
       </c>
@@ -20618,7 +20623,7 @@
       </c>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:71" ht="14.45">
+    <row r="16" spans="1:71" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>42401</v>
       </c>
@@ -20697,7 +20702,7 @@
       </c>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" ht="14.45">
+    <row r="17" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>42430</v>
       </c>
@@ -20776,7 +20781,7 @@
       </c>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" ht="14.45">
+    <row r="18" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>42461</v>
       </c>
@@ -20855,7 +20860,7 @@
       </c>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" ht="14.45">
+    <row r="19" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>42491</v>
       </c>
@@ -20934,7 +20939,7 @@
       </c>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" ht="14.45">
+    <row r="20" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>42522</v>
       </c>
@@ -21013,7 +21018,7 @@
       </c>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" ht="14.45">
+    <row r="21" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>42552</v>
       </c>
@@ -21092,7 +21097,7 @@
       </c>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" ht="14.45">
+    <row r="22" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>42583</v>
       </c>
@@ -21171,7 +21176,7 @@
       </c>
       <c r="Y22" s="3"/>
     </row>
-    <row r="23" spans="1:25" ht="14.45">
+    <row r="23" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>42614</v>
       </c>
@@ -21250,7 +21255,7 @@
       </c>
       <c r="Y23" s="3"/>
     </row>
-    <row r="24" spans="1:25" ht="14.45">
+    <row r="24" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>42644</v>
       </c>
@@ -21329,7 +21334,7 @@
       </c>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" ht="14.45">
+    <row r="25" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>42675</v>
       </c>
@@ -21408,7 +21413,7 @@
       </c>
       <c r="Y25" s="3"/>
     </row>
-    <row r="26" spans="1:25" ht="14.45">
+    <row r="26" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>42705</v>
       </c>
@@ -21487,7 +21492,7 @@
       </c>
       <c r="Y26" s="3"/>
     </row>
-    <row r="27" spans="1:25" ht="14.45">
+    <row r="27" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>42736</v>
       </c>
@@ -21566,7 +21571,7 @@
       </c>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" ht="14.45">
+    <row r="28" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>42767</v>
       </c>
@@ -21645,7 +21650,7 @@
       </c>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" spans="1:25" ht="14.45">
+    <row r="29" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>42795</v>
       </c>
@@ -21724,7 +21729,7 @@
       </c>
       <c r="Y29" s="3"/>
     </row>
-    <row r="30" spans="1:25" ht="14.45">
+    <row r="30" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>42826</v>
       </c>
@@ -21803,7 +21808,7 @@
       </c>
       <c r="Y30" s="3"/>
     </row>
-    <row r="31" spans="1:25" ht="14.45">
+    <row r="31" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>42856</v>
       </c>
@@ -21882,7 +21887,7 @@
       </c>
       <c r="Y31" s="3"/>
     </row>
-    <row r="32" spans="1:25" ht="14.45">
+    <row r="32" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>42887</v>
       </c>
@@ -21961,7 +21966,7 @@
       </c>
       <c r="Y32" s="3"/>
     </row>
-    <row r="33" spans="1:25" ht="14.45">
+    <row r="33" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>42917</v>
       </c>
@@ -22040,7 +22045,7 @@
       </c>
       <c r="Y33" s="3"/>
     </row>
-    <row r="34" spans="1:25" ht="14.45">
+    <row r="34" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>42948</v>
       </c>
@@ -22119,7 +22124,7 @@
       </c>
       <c r="Y34" s="3"/>
     </row>
-    <row r="35" spans="1:25" ht="14.45">
+    <row r="35" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>42979</v>
       </c>
@@ -22198,7 +22203,7 @@
       </c>
       <c r="Y35" s="3"/>
     </row>
-    <row r="36" spans="1:25" ht="14.45">
+    <row r="36" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>43009</v>
       </c>
@@ -22277,7 +22282,7 @@
       </c>
       <c r="Y36" s="3"/>
     </row>
-    <row r="37" spans="1:25" ht="14.45">
+    <row r="37" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>43040</v>
       </c>
@@ -22356,7 +22361,7 @@
       </c>
       <c r="Y37" s="3"/>
     </row>
-    <row r="38" spans="1:25" ht="14.45">
+    <row r="38" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>43070</v>
       </c>
@@ -22435,7 +22440,7 @@
       </c>
       <c r="Y38" s="3"/>
     </row>
-    <row r="39" spans="1:25" ht="14.45">
+    <row r="39" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>43101</v>
       </c>
@@ -22514,7 +22519,7 @@
       </c>
       <c r="Y39" s="3"/>
     </row>
-    <row r="40" spans="1:25" ht="14.45">
+    <row r="40" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>43132</v>
       </c>
@@ -22593,7 +22598,7 @@
       </c>
       <c r="Y40" s="3"/>
     </row>
-    <row r="41" spans="1:25" ht="14.45">
+    <row r="41" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>43160</v>
       </c>
@@ -22672,7 +22677,7 @@
       </c>
       <c r="Y41" s="3"/>
     </row>
-    <row r="42" spans="1:25" ht="14.45">
+    <row r="42" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>43191</v>
       </c>
@@ -22751,7 +22756,7 @@
       </c>
       <c r="Y42" s="3"/>
     </row>
-    <row r="43" spans="1:25" ht="14.45">
+    <row r="43" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>43221</v>
       </c>
@@ -22830,7 +22835,7 @@
       </c>
       <c r="Y43" s="3"/>
     </row>
-    <row r="44" spans="1:25" ht="14.45">
+    <row r="44" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>43252</v>
       </c>
@@ -22909,7 +22914,7 @@
       </c>
       <c r="Y44" s="3"/>
     </row>
-    <row r="45" spans="1:25" ht="14.45">
+    <row r="45" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>43282</v>
       </c>
@@ -22988,7 +22993,7 @@
       </c>
       <c r="Y45" s="3"/>
     </row>
-    <row r="46" spans="1:25" ht="14.45">
+    <row r="46" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>43313</v>
       </c>
@@ -23067,7 +23072,7 @@
       </c>
       <c r="Y46" s="3"/>
     </row>
-    <row r="47" spans="1:25" ht="14.45">
+    <row r="47" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>43344</v>
       </c>
@@ -23146,7 +23151,7 @@
       </c>
       <c r="Y47" s="3"/>
     </row>
-    <row r="48" spans="1:25" ht="14.45">
+    <row r="48" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>43374</v>
       </c>
@@ -23225,7 +23230,7 @@
       </c>
       <c r="Y48" s="3"/>
     </row>
-    <row r="49" spans="1:25" ht="14.45">
+    <row r="49" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>43405</v>
       </c>
@@ -23304,7 +23309,7 @@
       </c>
       <c r="Y49" s="3"/>
     </row>
-    <row r="50" spans="1:25" ht="14.45">
+    <row r="50" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>43435</v>
       </c>
@@ -23383,7 +23388,7 @@
       </c>
       <c r="Y50" s="3"/>
     </row>
-    <row r="51" spans="1:25" ht="14.45">
+    <row r="51" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>43466</v>
       </c>
@@ -23462,7 +23467,7 @@
       </c>
       <c r="Y51" s="3"/>
     </row>
-    <row r="52" spans="1:25" ht="14.45">
+    <row r="52" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>43497</v>
       </c>
@@ -23541,7 +23546,7 @@
       </c>
       <c r="Y52" s="3"/>
     </row>
-    <row r="53" spans="1:25" ht="14.45">
+    <row r="53" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43525</v>
       </c>
@@ -23620,7 +23625,7 @@
       </c>
       <c r="Y53" s="3"/>
     </row>
-    <row r="54" spans="1:25" ht="14.45">
+    <row r="54" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>43556</v>
       </c>
@@ -23699,7 +23704,7 @@
       </c>
       <c r="Y54" s="3"/>
     </row>
-    <row r="55" spans="1:25" ht="14.45">
+    <row r="55" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43586</v>
       </c>
@@ -23778,7 +23783,7 @@
       </c>
       <c r="Y55" s="3"/>
     </row>
-    <row r="56" spans="1:25" ht="14.45">
+    <row r="56" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>43617</v>
       </c>
@@ -23857,7 +23862,7 @@
       </c>
       <c r="Y56" s="3"/>
     </row>
-    <row r="57" spans="1:25" ht="14.45">
+    <row r="57" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43647</v>
       </c>
@@ -23936,7 +23941,7 @@
       </c>
       <c r="Y57" s="3"/>
     </row>
-    <row r="58" spans="1:25" ht="14.45">
+    <row r="58" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>43678</v>
       </c>
@@ -24015,7 +24020,7 @@
       </c>
       <c r="Y58" s="3"/>
     </row>
-    <row r="59" spans="1:25" ht="14.45">
+    <row r="59" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43709</v>
       </c>
@@ -24094,7 +24099,7 @@
       </c>
       <c r="Y59" s="3"/>
     </row>
-    <row r="60" spans="1:25" ht="14.45">
+    <row r="60" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>43739</v>
       </c>
@@ -24173,7 +24178,7 @@
       </c>
       <c r="Y60" s="3"/>
     </row>
-    <row r="61" spans="1:25" ht="14.45">
+    <row r="61" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43770</v>
       </c>
@@ -24252,7 +24257,7 @@
       </c>
       <c r="Y61" s="3"/>
     </row>
-    <row r="62" spans="1:25" ht="14.45">
+    <row r="62" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>43800</v>
       </c>
@@ -24331,7 +24336,7 @@
       </c>
       <c r="Y62" s="3"/>
     </row>
-    <row r="63" spans="1:25" ht="14.45">
+    <row r="63" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43831</v>
       </c>
@@ -24410,7 +24415,7 @@
       </c>
       <c r="Y63" s="3"/>
     </row>
-    <row r="64" spans="1:25" ht="14.45">
+    <row r="64" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>43862</v>
       </c>
@@ -24489,7 +24494,7 @@
       </c>
       <c r="Y64" s="3"/>
     </row>
-    <row r="65" spans="1:25" ht="14.45">
+    <row r="65" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43891</v>
       </c>
@@ -24568,7 +24573,7 @@
       </c>
       <c r="Y65" s="3"/>
     </row>
-    <row r="66" spans="1:25" ht="14.45">
+    <row r="66" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>43922</v>
       </c>
@@ -24647,7 +24652,7 @@
       </c>
       <c r="Y66" s="3"/>
     </row>
-    <row r="67" spans="1:25" ht="14.45">
+    <row r="67" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43952</v>
       </c>
@@ -24726,7 +24731,7 @@
       </c>
       <c r="Y67" s="3"/>
     </row>
-    <row r="68" spans="1:25" ht="14.45">
+    <row r="68" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>43983</v>
       </c>
@@ -24805,7 +24810,7 @@
       </c>
       <c r="Y68" s="3"/>
     </row>
-    <row r="69" spans="1:25" ht="14.45">
+    <row r="69" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>44013</v>
       </c>
@@ -24884,7 +24889,7 @@
       </c>
       <c r="Y69" s="3"/>
     </row>
-    <row r="70" spans="1:25" ht="14.45">
+    <row r="70" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>44044</v>
       </c>
@@ -24963,7 +24968,7 @@
       </c>
       <c r="Y70" s="3"/>
     </row>
-    <row r="71" spans="1:25" ht="14.45">
+    <row r="71" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>44075</v>
       </c>
@@ -25042,7 +25047,7 @@
       </c>
       <c r="Y71" s="3"/>
     </row>
-    <row r="72" spans="1:25" ht="14.45">
+    <row r="72" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>44105</v>
       </c>
@@ -25121,7 +25126,7 @@
       </c>
       <c r="Y72" s="3"/>
     </row>
-    <row r="73" spans="1:25" ht="14.45">
+    <row r="73" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>44136</v>
       </c>
@@ -25200,7 +25205,7 @@
       </c>
       <c r="Y73" s="3"/>
     </row>
-    <row r="74" spans="1:25" ht="14.45">
+    <row r="74" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>44166</v>
       </c>
@@ -25279,7 +25284,7 @@
       </c>
       <c r="Y74" s="3"/>
     </row>
-    <row r="75" spans="1:25" ht="14.45">
+    <row r="75" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>44197</v>
       </c>
@@ -25358,7 +25363,7 @@
       </c>
       <c r="Y75" s="3"/>
     </row>
-    <row r="76" spans="1:25" ht="14.45">
+    <row r="76" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>44228</v>
       </c>
@@ -25437,7 +25442,7 @@
       </c>
       <c r="Y76" s="3"/>
     </row>
-    <row r="77" spans="1:25" ht="14.45">
+    <row r="77" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>44256</v>
       </c>
@@ -25516,7 +25521,7 @@
       </c>
       <c r="Y77" s="3"/>
     </row>
-    <row r="78" spans="1:25" ht="14.45">
+    <row r="78" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>44287</v>
       </c>
@@ -25595,7 +25600,7 @@
       </c>
       <c r="Y78" s="3"/>
     </row>
-    <row r="79" spans="1:25" ht="14.45">
+    <row r="79" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>44317</v>
       </c>
@@ -25674,7 +25679,7 @@
       </c>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" spans="1:25" ht="14.45">
+    <row r="80" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>44348</v>
       </c>
@@ -25753,7 +25758,7 @@
       </c>
       <c r="Y80" s="3"/>
     </row>
-    <row r="81" spans="1:25" ht="14.45">
+    <row r="81" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>44378</v>
       </c>
@@ -25832,7 +25837,7 @@
       </c>
       <c r="Y81" s="3"/>
     </row>
-    <row r="82" spans="1:25" ht="14.45">
+    <row r="82" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>44409</v>
       </c>
@@ -25911,7 +25916,7 @@
       </c>
       <c r="Y82" s="3"/>
     </row>
-    <row r="83" spans="1:25" ht="14.45">
+    <row r="83" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>44440</v>
       </c>
@@ -25990,7 +25995,7 @@
       </c>
       <c r="Y83" s="3"/>
     </row>
-    <row r="84" spans="1:25" ht="14.45">
+    <row r="84" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>44470</v>
       </c>
@@ -26069,7 +26074,7 @@
       </c>
       <c r="Y84" s="3"/>
     </row>
-    <row r="85" spans="1:25" ht="14.45">
+    <row r="85" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>44501</v>
       </c>
@@ -26148,7 +26153,7 @@
       </c>
       <c r="Y85" s="3"/>
     </row>
-    <row r="86" spans="1:25" ht="14.45">
+    <row r="86" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>44531</v>
       </c>
@@ -26227,7 +26232,7 @@
       </c>
       <c r="Y86" s="3"/>
     </row>
-    <row r="87" spans="1:25" ht="14.45">
+    <row r="87" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>44562</v>
       </c>
@@ -26306,7 +26311,7 @@
       </c>
       <c r="Y87" s="3"/>
     </row>
-    <row r="88" spans="1:25" ht="14.45">
+    <row r="88" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>44593</v>
       </c>
@@ -26385,7 +26390,7 @@
       </c>
       <c r="Y88" s="3"/>
     </row>
-    <row r="89" spans="1:25" ht="14.45">
+    <row r="89" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>44621</v>
       </c>
@@ -26464,7 +26469,7 @@
       </c>
       <c r="Y89" s="3"/>
     </row>
-    <row r="90" spans="1:25" ht="14.45">
+    <row r="90" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>44652</v>
       </c>
@@ -26543,7 +26548,7 @@
       </c>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" spans="1:25" ht="14.45">
+    <row r="91" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>44682</v>
       </c>
@@ -26622,7 +26627,7 @@
       </c>
       <c r="Y91" s="3"/>
     </row>
-    <row r="92" spans="1:25" ht="14.45">
+    <row r="92" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>44713</v>
       </c>
@@ -26701,7 +26706,7 @@
       </c>
       <c r="Y92" s="3"/>
     </row>
-    <row r="93" spans="1:25" ht="14.45">
+    <row r="93" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>44743</v>
       </c>
@@ -26780,7 +26785,7 @@
       </c>
       <c r="Y93" s="3"/>
     </row>
-    <row r="94" spans="1:25" ht="14.45">
+    <row r="94" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>44774</v>
       </c>
@@ -26859,7 +26864,7 @@
       </c>
       <c r="Y94" s="3"/>
     </row>
-    <row r="95" spans="1:25" ht="14.45">
+    <row r="95" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>44805</v>
       </c>
@@ -26938,7 +26943,7 @@
       </c>
       <c r="Y95" s="3"/>
     </row>
-    <row r="96" spans="1:25" ht="14.45">
+    <row r="96" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>44835</v>
       </c>
@@ -27017,7 +27022,7 @@
       </c>
       <c r="Y96" s="3"/>
     </row>
-    <row r="97" spans="1:25" ht="14.45">
+    <row r="97" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>44866</v>
       </c>
@@ -27096,7 +27101,7 @@
       </c>
       <c r="Y97" s="3"/>
     </row>
-    <row r="98" spans="1:25" ht="14.45">
+    <row r="98" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>44896</v>
       </c>
@@ -27175,7 +27180,7 @@
       </c>
       <c r="Y98" s="3"/>
     </row>
-    <row r="99" spans="1:25" ht="14.45">
+    <row r="99" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>44927</v>
       </c>
@@ -27254,7 +27259,7 @@
       </c>
       <c r="Y99" s="3"/>
     </row>
-    <row r="100" spans="1:25" ht="14.45">
+    <row r="100" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>44958</v>
       </c>
@@ -27305,7 +27310,7 @@
       </c>
       <c r="Y100" s="3"/>
     </row>
-    <row r="101" spans="1:25" ht="14.45">
+    <row r="101" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>44986</v>
       </c>
@@ -27356,7 +27361,7 @@
       </c>
       <c r="Y101" s="3"/>
     </row>
-    <row r="102" spans="1:25" ht="14.45">
+    <row r="102" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>45017</v>
       </c>
@@ -27407,7 +27412,7 @@
       </c>
       <c r="Y102" s="3"/>
     </row>
-    <row r="103" spans="1:25" ht="14.45">
+    <row r="103" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>45047</v>
       </c>
@@ -27458,7 +27463,7 @@
       </c>
       <c r="Y103" s="3"/>
     </row>
-    <row r="104" spans="1:25" ht="14.45">
+    <row r="104" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>45078</v>
       </c>
@@ -27509,7 +27514,7 @@
       </c>
       <c r="Y104" s="3"/>
     </row>
-    <row r="105" spans="1:25" ht="14.45">
+    <row r="105" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>45108</v>
       </c>
@@ -27560,7 +27565,7 @@
       </c>
       <c r="Y105" s="3"/>
     </row>
-    <row r="106" spans="1:25" ht="14.45">
+    <row r="106" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>45139</v>
       </c>
@@ -27611,7 +27616,7 @@
       </c>
       <c r="Y106" s="3"/>
     </row>
-    <row r="107" spans="1:25" ht="14.45">
+    <row r="107" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>45170</v>
       </c>
@@ -27662,7 +27667,7 @@
       </c>
       <c r="Y107" s="3"/>
     </row>
-    <row r="108" spans="1:25" ht="14.45">
+    <row r="108" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>45200</v>
       </c>
@@ -27713,7 +27718,7 @@
       </c>
       <c r="Y108" s="3"/>
     </row>
-    <row r="109" spans="1:25" ht="14.45">
+    <row r="109" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>45231</v>
       </c>
@@ -27764,7 +27769,7 @@
       </c>
       <c r="Y109" s="3"/>
     </row>
-    <row r="110" spans="1:25" ht="14.45">
+    <row r="110" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>45261</v>
       </c>
@@ -27815,7 +27820,7 @@
       </c>
       <c r="Y110" s="3"/>
     </row>
-    <row r="111" spans="1:25" ht="14.45">
+    <row r="111" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>45292</v>
       </c>
@@ -27866,7 +27871,7 @@
       </c>
       <c r="Y111" s="3"/>
     </row>
-    <row r="112" spans="1:25" ht="14.45">
+    <row r="112" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>45323</v>
       </c>
@@ -27917,7 +27922,7 @@
       </c>
       <c r="Y112" s="3"/>
     </row>
-    <row r="113" spans="1:25" ht="14.45">
+    <row r="113" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>45352</v>
       </c>
@@ -27968,7 +27973,7 @@
       </c>
       <c r="Y113" s="3"/>
     </row>
-    <row r="114" spans="1:25" ht="14.45">
+    <row r="114" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>45383</v>
       </c>
@@ -28019,7 +28024,7 @@
       </c>
       <c r="Y114" s="3"/>
     </row>
-    <row r="115" spans="1:25" ht="14.45">
+    <row r="115" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>45413</v>
       </c>
@@ -28070,7 +28075,7 @@
       </c>
       <c r="Y115" s="3"/>
     </row>
-    <row r="116" spans="1:25" ht="14.45">
+    <row r="116" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>45444</v>
       </c>
@@ -28121,7 +28126,7 @@
       </c>
       <c r="Y116" s="3"/>
     </row>
-    <row r="117" spans="1:25" ht="14.45">
+    <row r="117" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>45474</v>
       </c>
@@ -28172,7 +28177,7 @@
       </c>
       <c r="Y117" s="3"/>
     </row>
-    <row r="118" spans="1:25" ht="14.45">
+    <row r="118" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>45505</v>
       </c>
@@ -28223,7 +28228,7 @@
       </c>
       <c r="Y118" s="3"/>
     </row>
-    <row r="119" spans="1:25" ht="14.45">
+    <row r="119" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>45536</v>
       </c>
@@ -28274,7 +28279,7 @@
       </c>
       <c r="Y119" s="3"/>
     </row>
-    <row r="120" spans="1:25" ht="14.45">
+    <row r="120" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>45566</v>
       </c>
@@ -28325,7 +28330,7 @@
       </c>
       <c r="Y120" s="3"/>
     </row>
-    <row r="121" spans="1:25" ht="14.45">
+    <row r="121" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>45597</v>
       </c>
@@ -28376,7 +28381,7 @@
       </c>
       <c r="Y121" s="3"/>
     </row>
-    <row r="122" spans="1:25" ht="14.45">
+    <row r="122" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>45627</v>
       </c>
@@ -28427,7 +28432,7 @@
       </c>
       <c r="Y122" s="3"/>
     </row>
-    <row r="123" spans="1:25" ht="14.45">
+    <row r="123" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>45658</v>
       </c>
@@ -28478,7 +28483,7 @@
       </c>
       <c r="Y123" s="3"/>
     </row>
-    <row r="124" spans="1:25" ht="14.45">
+    <row r="124" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>45689</v>
       </c>
@@ -28529,7 +28534,7 @@
       </c>
       <c r="Y124" s="3"/>
     </row>
-    <row r="125" spans="1:25" ht="14.45">
+    <row r="125" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>45717</v>
       </c>
@@ -28580,7 +28585,7 @@
       </c>
       <c r="Y125" s="3"/>
     </row>
-    <row r="126" spans="1:25" ht="14.45">
+    <row r="126" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>45748</v>
       </c>
@@ -28631,7 +28636,7 @@
       </c>
       <c r="Y126" s="3"/>
     </row>
-    <row r="127" spans="1:25" ht="14.45">
+    <row r="127" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>45778</v>
       </c>
@@ -28682,7 +28687,7 @@
       </c>
       <c r="Y127" s="3"/>
     </row>
-    <row r="128" spans="1:25" ht="14.45">
+    <row r="128" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>45809</v>
       </c>
@@ -28733,7 +28738,7 @@
       </c>
       <c r="Y128" s="3"/>
     </row>
-    <row r="129" spans="1:25" ht="14.45">
+    <row r="129" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>45839</v>
       </c>
@@ -28782,7 +28787,7 @@
       <c r="X129" s="27"/>
       <c r="Y129" s="3"/>
     </row>
-    <row r="130" spans="1:25" ht="14.45">
+    <row r="130" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>45870</v>
       </c>
@@ -28831,7 +28836,7 @@
       <c r="X130" s="27"/>
       <c r="Y130" s="3"/>
     </row>
-    <row r="131" spans="1:25" ht="14.45">
+    <row r="131" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>45901</v>
       </c>
@@ -28865,7 +28870,7 @@
       <c r="X131" s="27"/>
       <c r="Y131" s="3"/>
     </row>
-    <row r="132" spans="1:25" ht="14.45">
+    <row r="132" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>45931</v>
       </c>
@@ -28899,7 +28904,7 @@
       <c r="X132" s="27"/>
       <c r="Y132" s="3"/>
     </row>
-    <row r="133" spans="1:25" ht="14.45">
+    <row r="133" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>45962</v>
       </c>
@@ -28933,7 +28938,7 @@
       <c r="X133" s="27"/>
       <c r="Y133" s="3"/>
     </row>
-    <row r="134" spans="1:25" ht="14.45">
+    <row r="134" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>45992</v>
       </c>
@@ -28967,7 +28972,7 @@
       <c r="X134" s="27"/>
       <c r="Y134" s="3"/>
     </row>
-    <row r="135" spans="1:25" ht="14.45">
+    <row r="135" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
       <c r="P135" s="27"/>
       <c r="Q135" s="27"/>
@@ -28982,7 +28987,7 @@
       </c>
       <c r="W135" s="27"/>
     </row>
-    <row r="136" spans="1:25" ht="14.45">
+    <row r="136" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="S136" s="28">
         <v>1361.3369666666699</v>
       </c>
@@ -28996,25 +29001,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC130"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.85546875" style="16" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="16" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" style="16" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.88671875" style="16" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" style="16" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" style="16" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" style="16" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.7109375" customWidth="1"/>
-    <col min="29" max="29" width="10.7109375" customWidth="1"/>
+    <col min="22" max="22" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="14.45" customHeight="1">
+    <row r="1" spans="1:29" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B1" s="4">
         <v>1</v>
@@ -29101,96 +29106,96 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="7" customFormat="1">
+    <row r="2" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="15" t="s">
-        <v>12</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="X2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="AC2" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>42005</v>
       </c>
@@ -29268,7 +29273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>42036</v>
       </c>
@@ -29366,7 +29371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>42064</v>
       </c>
@@ -29464,7 +29469,7 @@
         <v>1.0048143053645116</v>
       </c>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>42095</v>
       </c>
@@ -29562,7 +29567,7 @@
         <v>0.99862448418156802</v>
       </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>42125</v>
       </c>
@@ -29660,7 +29665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>42156</v>
       </c>
@@ -29758,7 +29763,7 @@
         <v>0.99587345254470427</v>
       </c>
     </row>
-    <row r="9" spans="1:29">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>42186</v>
       </c>
@@ -29856,7 +29861,7 @@
         <v>1.0055020632737275</v>
       </c>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>42217</v>
       </c>
@@ -29954,7 +29959,7 @@
         <v>0.99793672627235208</v>
       </c>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>42248</v>
       </c>
@@ -30052,7 +30057,7 @@
         <v>0.98555708390646501</v>
       </c>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>42278</v>
       </c>
@@ -30150,7 +30155,7 @@
         <v>0.98555708390646501</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>42309</v>
       </c>
@@ -30248,7 +30253,7 @@
         <v>0.98555708390646501</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>42339</v>
       </c>
@@ -30346,7 +30351,7 @@
         <v>0.98555708390646501</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>42370</v>
       </c>
@@ -30444,7 +30449,7 @@
         <v>0.98349381017881699</v>
       </c>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>42401</v>
       </c>
@@ -30542,7 +30547,7 @@
         <v>0.98349381017881699</v>
       </c>
     </row>
-    <row r="17" spans="1:29">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>42430</v>
       </c>
@@ -30640,7 +30645,7 @@
         <v>0.969050894085282</v>
       </c>
     </row>
-    <row r="18" spans="1:29">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>42461</v>
       </c>
@@ -30738,7 +30743,7 @@
         <v>0.969050894085282</v>
       </c>
     </row>
-    <row r="19" spans="1:29">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>42491</v>
       </c>
@@ -30836,7 +30841,7 @@
         <v>0.969050894085282</v>
       </c>
     </row>
-    <row r="20" spans="1:29">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>42522</v>
       </c>
@@ -30934,7 +30939,7 @@
         <v>0.969050894085282</v>
       </c>
     </row>
-    <row r="21" spans="1:29">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>42552</v>
       </c>
@@ -31032,7 +31037,7 @@
         <v>0.969050894085282</v>
       </c>
     </row>
-    <row r="22" spans="1:29">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>42583</v>
       </c>
@@ -31130,7 +31135,7 @@
         <v>0.969050894085282</v>
       </c>
     </row>
-    <row r="23" spans="1:29">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>42614</v>
       </c>
@@ -31228,7 +31233,7 @@
         <v>0.96492434662998627</v>
       </c>
     </row>
-    <row r="24" spans="1:29">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>42644</v>
       </c>
@@ -31326,7 +31331,7 @@
         <v>0.96492434662998627</v>
       </c>
     </row>
-    <row r="25" spans="1:29">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>42675</v>
       </c>
@@ -31424,7 +31429,7 @@
         <v>0.96492434662998627</v>
       </c>
     </row>
-    <row r="26" spans="1:29">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>42705</v>
       </c>
@@ -31522,7 +31527,7 @@
         <v>0.96836313617606606</v>
       </c>
     </row>
-    <row r="27" spans="1:29">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>42736</v>
       </c>
@@ -31620,7 +31625,7 @@
         <v>0.96836313617606606</v>
       </c>
     </row>
-    <row r="28" spans="1:29">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>42767</v>
       </c>
@@ -31718,7 +31723,7 @@
         <v>0.96836313617606606</v>
       </c>
     </row>
-    <row r="29" spans="1:29">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>42795</v>
       </c>
@@ -31816,7 +31821,7 @@
         <v>0.96836313617606606</v>
       </c>
     </row>
-    <row r="30" spans="1:29">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>42826</v>
       </c>
@@ -31914,7 +31919,7 @@
         <v>0.98555708390646501</v>
       </c>
     </row>
-    <row r="31" spans="1:29">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>42856</v>
       </c>
@@ -32012,7 +32017,7 @@
         <v>0.98555708390646501</v>
       </c>
     </row>
-    <row r="32" spans="1:29">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>42887</v>
       </c>
@@ -32110,7 +32115,7 @@
         <v>0.98555708390646501</v>
       </c>
     </row>
-    <row r="33" spans="1:29">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>42917</v>
       </c>
@@ -32208,7 +32213,7 @@
         <v>0.98555708390646501</v>
       </c>
     </row>
-    <row r="34" spans="1:29">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>42948</v>
       </c>
@@ -32306,7 +32311,7 @@
         <v>0.98762035763411271</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>42979</v>
       </c>
@@ -32404,7 +32409,7 @@
         <v>0.98762035763411271</v>
       </c>
     </row>
-    <row r="36" spans="1:29">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>43009</v>
       </c>
@@ -32502,7 +32507,7 @@
         <v>0.98762035763411271</v>
       </c>
     </row>
-    <row r="37" spans="1:29">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>43040</v>
       </c>
@@ -32600,7 +32605,7 @@
         <v>1.0392022008253095</v>
       </c>
     </row>
-    <row r="38" spans="1:29">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>43070</v>
       </c>
@@ -32698,7 +32703,7 @@
         <v>1.0392022008253095</v>
       </c>
     </row>
-    <row r="39" spans="1:29">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>43101</v>
       </c>
@@ -32796,7 +32801,7 @@
         <v>1.0392022008253095</v>
       </c>
     </row>
-    <row r="40" spans="1:29">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>43132</v>
       </c>
@@ -32894,7 +32899,7 @@
         <v>1.0392022008253095</v>
       </c>
     </row>
-    <row r="41" spans="1:29">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>43160</v>
       </c>
@@ -32992,7 +32997,7 @@
         <v>1.0502063273727646</v>
       </c>
     </row>
-    <row r="42" spans="1:29">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>43191</v>
       </c>
@@ -33090,7 +33095,7 @@
         <v>1.0997248968363136</v>
       </c>
     </row>
-    <row r="43" spans="1:29">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>43221</v>
       </c>
@@ -33188,7 +33193,7 @@
         <v>1.0997248968363136</v>
       </c>
     </row>
-    <row r="44" spans="1:29">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>43252</v>
       </c>
@@ -33286,7 +33291,7 @@
         <v>1.0935350756533699</v>
       </c>
     </row>
-    <row r="45" spans="1:29">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>43282</v>
       </c>
@@ -33384,7 +33389,7 @@
         <v>1.1196698762035764</v>
       </c>
     </row>
-    <row r="46" spans="1:29">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>43313</v>
       </c>
@@ -33482,7 +33487,7 @@
         <v>1.1196698762035764</v>
       </c>
     </row>
-    <row r="47" spans="1:29">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>43344</v>
       </c>
@@ -33580,7 +33585,7 @@
         <v>1.1196698762035764</v>
       </c>
     </row>
-    <row r="48" spans="1:29">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>43374</v>
       </c>
@@ -33678,7 +33683,7 @@
         <v>1.1196698762035764</v>
       </c>
     </row>
-    <row r="49" spans="1:29">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>43405</v>
       </c>
@@ -33776,7 +33781,7 @@
         <v>1.1196698762035764</v>
       </c>
     </row>
-    <row r="50" spans="1:29">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>43435</v>
       </c>
@@ -33874,7 +33879,7 @@
         <v>1.1196698762035764</v>
       </c>
     </row>
-    <row r="51" spans="1:29">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>43466</v>
       </c>
@@ -33972,7 +33977,7 @@
         <v>1.1182943603851443</v>
       </c>
     </row>
-    <row r="52" spans="1:29">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>43497</v>
       </c>
@@ -34070,7 +34075,7 @@
         <v>1.1196698762035764</v>
       </c>
     </row>
-    <row r="53" spans="1:29">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43525</v>
       </c>
@@ -34168,7 +34173,7 @@
         <v>1.1224209078404401</v>
       </c>
     </row>
-    <row r="54" spans="1:29">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>43556</v>
       </c>
@@ -34266,7 +34271,7 @@
         <v>1.1224209078404401</v>
       </c>
     </row>
-    <row r="55" spans="1:29">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43586</v>
       </c>
@@ -34364,7 +34369,7 @@
         <v>1.1004126547455295</v>
       </c>
     </row>
-    <row r="56" spans="1:29">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>43617</v>
       </c>
@@ -34462,7 +34467,7 @@
         <v>1.0646492434663</v>
       </c>
     </row>
-    <row r="57" spans="1:29">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43647</v>
       </c>
@@ -34560,7 +34565,7 @@
         <v>1.0646492434663</v>
       </c>
     </row>
-    <row r="58" spans="1:29">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>43678</v>
       </c>
@@ -34658,7 +34663,7 @@
         <v>1.0646492434663</v>
       </c>
     </row>
-    <row r="59" spans="1:29">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43709</v>
       </c>
@@ -34756,7 +34761,7 @@
         <v>1.0646492434663</v>
       </c>
     </row>
-    <row r="60" spans="1:29">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>43739</v>
       </c>
@@ -34854,7 +34859,7 @@
         <v>1.0646492434663</v>
       </c>
     </row>
-    <row r="61" spans="1:29">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43770</v>
       </c>
@@ -34952,7 +34957,7 @@
         <v>1.0625859697386519</v>
       </c>
     </row>
-    <row r="62" spans="1:29">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>43800</v>
       </c>
@@ -35050,7 +35055,7 @@
         <v>1.0612104539202201</v>
       </c>
     </row>
-    <row r="63" spans="1:29">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43831</v>
       </c>
@@ -35148,7 +35153,7 @@
         <v>1.0426409903713891</v>
       </c>
     </row>
-    <row r="64" spans="1:29">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>43862</v>
       </c>
@@ -35246,7 +35251,7 @@
         <v>1.0398899587345254</v>
       </c>
     </row>
-    <row r="65" spans="1:29">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43891</v>
       </c>
@@ -35344,7 +35349,7 @@
         <v>1.0357634112792296</v>
       </c>
     </row>
-    <row r="66" spans="1:29">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>43922</v>
       </c>
@@ -35442,7 +35447,7 @@
         <v>1.0357634112792296</v>
       </c>
     </row>
-    <row r="67" spans="1:29">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43952</v>
       </c>
@@ -35540,7 +35545,7 @@
         <v>1.0357634112792296</v>
       </c>
     </row>
-    <row r="68" spans="1:29">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>43983</v>
       </c>
@@ -35638,7 +35643,7 @@
         <v>1.0357634112792296</v>
       </c>
     </row>
-    <row r="69" spans="1:29">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>44013</v>
       </c>
@@ -35736,7 +35741,7 @@
         <v>1.0357634112792296</v>
       </c>
     </row>
-    <row r="70" spans="1:29">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>44044</v>
       </c>
@@ -35834,7 +35839,7 @@
         <v>0.95598349381017877</v>
       </c>
     </row>
-    <row r="71" spans="1:29">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>44075</v>
       </c>
@@ -35932,7 +35937,7 @@
         <v>0.94979367262723513</v>
       </c>
     </row>
-    <row r="72" spans="1:29">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>44105</v>
       </c>
@@ -36030,7 +36035,7 @@
         <v>0.88308115543328747</v>
       </c>
     </row>
-    <row r="73" spans="1:29">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>44136</v>
       </c>
@@ -36128,7 +36133,7 @@
         <v>0.87414030261347997</v>
       </c>
     </row>
-    <row r="74" spans="1:29">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>44166</v>
       </c>
@@ -36226,7 +36231,7 @@
         <v>0.86451169188445665</v>
       </c>
     </row>
-    <row r="75" spans="1:29">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>44197</v>
       </c>
@@ -36324,7 +36329,7 @@
         <v>0.86451169188445665</v>
       </c>
     </row>
-    <row r="76" spans="1:29">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>44228</v>
       </c>
@@ -36422,7 +36427,7 @@
         <v>0.86932599724896842</v>
       </c>
     </row>
-    <row r="77" spans="1:29">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>44256</v>
       </c>
@@ -36520,7 +36525,7 @@
         <v>0.85557083906464926</v>
       </c>
     </row>
-    <row r="78" spans="1:29">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>44287</v>
       </c>
@@ -36618,7 +36623,7 @@
         <v>0.86588720770288863</v>
       </c>
     </row>
-    <row r="79" spans="1:29">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>44317</v>
       </c>
@@ -36716,7 +36721,7 @@
         <v>1.0275103163686383</v>
       </c>
     </row>
-    <row r="80" spans="1:29">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>44348</v>
       </c>
@@ -36814,7 +36819,7 @@
         <v>1.0962861072902339</v>
       </c>
     </row>
-    <row r="81" spans="1:29">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>44378</v>
       </c>
@@ -36912,7 +36917,7 @@
         <v>1.1351444291609354</v>
       </c>
     </row>
-    <row r="82" spans="1:29">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>44409</v>
       </c>
@@ -37010,7 +37015,7 @@
         <v>1.1351444291609354</v>
       </c>
     </row>
-    <row r="83" spans="1:29">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>44440</v>
       </c>
@@ -37108,7 +37113,7 @@
         <v>1.1436038514442917</v>
       </c>
     </row>
-    <row r="84" spans="1:29">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>44470</v>
       </c>
@@ -37206,7 +37211,7 @@
         <v>1.1737551581843191</v>
       </c>
     </row>
-    <row r="85" spans="1:29">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>44501</v>
       </c>
@@ -37304,7 +37309,7 @@
         <v>1.1720563961485557</v>
       </c>
     </row>
-    <row r="86" spans="1:29">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>44531</v>
       </c>
@@ -37402,7 +37407,7 @@
         <v>1.19328060522696</v>
       </c>
     </row>
-    <row r="87" spans="1:29">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>44562</v>
       </c>
@@ -37500,7 +37505,7 @@
         <v>1.2015887207702889</v>
       </c>
     </row>
-    <row r="88" spans="1:29">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>44593</v>
       </c>
@@ -37598,7 +37603,7 @@
         <v>1.1965199449793671</v>
       </c>
     </row>
-    <row r="89" spans="1:29">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>44621</v>
       </c>
@@ -37696,7 +37701,7 @@
         <v>1.2327235213204952</v>
       </c>
     </row>
-    <row r="90" spans="1:29">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>44652</v>
       </c>
@@ -37794,7 +37799,7 @@
         <v>1.2481636863823933</v>
       </c>
     </row>
-    <row r="91" spans="1:29">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>44682</v>
       </c>
@@ -37892,7 +37897,7 @@
         <v>1.2612242090784045</v>
       </c>
     </row>
-    <row r="92" spans="1:29">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>44713</v>
       </c>
@@ -37990,7 +37995,7 @@
         <v>1.2564442916093534</v>
       </c>
     </row>
-    <row r="93" spans="1:29">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>44743</v>
       </c>
@@ -38088,7 +38093,7 @@
         <v>1.2585694635488309</v>
       </c>
     </row>
-    <row r="94" spans="1:29">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>44774</v>
       </c>
@@ -38186,7 +38191,7 @@
         <v>1.21207015130674</v>
       </c>
     </row>
-    <row r="95" spans="1:29">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>44805</v>
       </c>
@@ -38284,7 +38289,7 @@
         <v>1.2023177441540578</v>
       </c>
     </row>
-    <row r="96" spans="1:29">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>44835</v>
       </c>
@@ -38382,7 +38387,7 @@
         <v>1.1714993122420909</v>
       </c>
     </row>
-    <row r="97" spans="1:29">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>44866</v>
       </c>
@@ -38480,7 +38485,7 @@
         <v>1.1617537826685007</v>
       </c>
     </row>
-    <row r="98" spans="1:29">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>44896</v>
       </c>
@@ -38578,7 +38583,7 @@
         <v>1.1649656121045391</v>
       </c>
     </row>
-    <row r="99" spans="1:29">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>44927</v>
       </c>
@@ -38676,7 +38681,7 @@
         <v>1.1634525447042641</v>
       </c>
     </row>
-    <row r="100" spans="1:29">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>44958</v>
       </c>
@@ -38746,7 +38751,7 @@
         <v>1.1441609353507565</v>
       </c>
     </row>
-    <row r="101" spans="1:29">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>44986</v>
       </c>
@@ -38816,7 +38821,7 @@
         <v>1.1453301237964237</v>
       </c>
     </row>
-    <row r="102" spans="1:29">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>45017</v>
       </c>
@@ -38886,7 +38891,7 @@
         <v>1.1177922971114167</v>
       </c>
     </row>
-    <row r="103" spans="1:29">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>45047</v>
       </c>
@@ -38956,7 +38961,7 @@
         <v>1.1082668500687758</v>
       </c>
     </row>
-    <row r="104" spans="1:29">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>45078</v>
       </c>
@@ -39026,7 +39031,7 @@
         <v>1.1088583218707015</v>
       </c>
     </row>
-    <row r="105" spans="1:29">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>45108</v>
       </c>
@@ -39096,7 +39101,7 @@
         <v>1.0996767537826684</v>
       </c>
     </row>
-    <row r="106" spans="1:29">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>45139</v>
       </c>
@@ -39166,7 +39171,7 @@
         <v>1.0943397524071525</v>
       </c>
     </row>
-    <row r="107" spans="1:29">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>45170</v>
       </c>
@@ -39236,7 +39241,7 @@
         <v>1.0781292984869324</v>
       </c>
     </row>
-    <row r="108" spans="1:29">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>45200</v>
       </c>
@@ -39306,7 +39311,7 @@
         <v>1.0781292984869324</v>
       </c>
     </row>
-    <row r="109" spans="1:29">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>45231</v>
       </c>
@@ -39376,7 +39381,7 @@
         <v>1.0697730398899585</v>
       </c>
     </row>
-    <row r="110" spans="1:29">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>45261</v>
       </c>
@@ -39446,7 +39451,7 @@
         <v>1.0697111416781293</v>
       </c>
     </row>
-    <row r="111" spans="1:29">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>45292</v>
       </c>
@@ -39516,7 +39521,7 @@
         <v>1.0697111416781293</v>
       </c>
     </row>
-    <row r="112" spans="1:29">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>45323</v>
       </c>
@@ -39586,7 +39591,7 @@
         <v>1.0729092159559834</v>
       </c>
     </row>
-    <row r="113" spans="1:29">
+    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>45352</v>
       </c>
@@ -39656,7 +39661,7 @@
         <v>1.0715337001375516</v>
       </c>
     </row>
-    <row r="114" spans="1:29">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>45383</v>
       </c>
@@ -39726,7 +39731,7 @@
         <v>1.0715337001375516</v>
       </c>
     </row>
-    <row r="115" spans="1:29">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>45413</v>
       </c>
@@ -39796,7 +39801,7 @@
         <v>1.0715337001375516</v>
       </c>
     </row>
-    <row r="116" spans="1:29">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>45444</v>
       </c>
@@ -39866,7 +39871,7 @@
         <v>1.0715337001375516</v>
       </c>
     </row>
-    <row r="117" spans="1:29">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>45474</v>
       </c>
@@ -39936,7 +39941,7 @@
         <v>1.0715337001375516</v>
       </c>
     </row>
-    <row r="118" spans="1:29">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>45505</v>
       </c>
@@ -40006,7 +40011,7 @@
         <v>1.0715337001375516</v>
       </c>
     </row>
-    <row r="119" spans="1:29">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>45536</v>
       </c>
@@ -40076,7 +40081,7 @@
         <v>1.0715337001375516</v>
       </c>
     </row>
-    <row r="120" spans="1:29">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>45566</v>
       </c>
@@ -40146,7 +40151,7 @@
         <v>1.0715337001375516</v>
       </c>
     </row>
-    <row r="121" spans="1:29">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>45597</v>
       </c>
@@ -40216,7 +40221,7 @@
         <v>1.0774415405777167</v>
       </c>
     </row>
-    <row r="122" spans="1:29">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>45627</v>
       </c>
@@ -40286,7 +40291,7 @@
         <v>1.0774415405777167</v>
       </c>
     </row>
-    <row r="123" spans="1:29">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>45658</v>
       </c>
@@ -40356,7 +40361,7 @@
         <v>1.0958940852819807</v>
       </c>
     </row>
-    <row r="124" spans="1:29">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>45689</v>
       </c>
@@ -40426,7 +40431,7 @@
         <v>1.0958940852819807</v>
       </c>
     </row>
-    <row r="125" spans="1:29">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>45717</v>
       </c>
@@ -40496,7 +40501,7 @@
         <v>1.0958940852819807</v>
       </c>
     </row>
-    <row r="126" spans="1:29">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>45748</v>
       </c>
@@ -40566,7 +40571,7 @@
         <v>1.0958940852819807</v>
       </c>
     </row>
-    <row r="127" spans="1:29">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>45778</v>
       </c>
@@ -40636,7 +40641,7 @@
         <v>1.0958940852819807</v>
       </c>
     </row>
-    <row r="128" spans="1:29">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>45809</v>
       </c>
@@ -40706,7 +40711,7 @@
         <v>1.0958940852819807</v>
       </c>
     </row>
-    <row r="129" spans="1:29">
+    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>45839</v>
       </c>
@@ -40770,7 +40775,7 @@
         <v>1.0958940852819807</v>
       </c>
     </row>
-    <row r="130" spans="1:29">
+    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>45870</v>
       </c>
@@ -40843,38 +40848,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D4A578-7FF3-47B7-B140-A91902BFD66E}">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="16.42578125" customWidth="1"/>
+    <col min="1" max="8" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="9" customFormat="1" ht="43.15">
+    <row r="1" spans="1:8" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2015</v>
       </c>
@@ -40900,7 +40905,7 @@
         <v>380.14677211911703</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2016</v>
       </c>
@@ -40926,7 +40931,7 @@
         <v>367.64176957902572</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2017</v>
       </c>
@@ -40952,7 +40957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2018</v>
       </c>
@@ -40978,7 +40983,7 @@
         <v>461.83685307030959</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2019</v>
       </c>
@@ -41004,7 +41009,7 @@
         <v>472.04281245882515</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2020</v>
       </c>
@@ -41030,7 +41035,7 @@
         <v>487.74441733483172</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2021</v>
       </c>
@@ -41056,7 +41061,7 @@
         <v>619.99967836945802</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2022</v>
       </c>
@@ -41082,7 +41087,7 @@
         <v>537.14328511496979</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2023</v>
       </c>
@@ -41108,7 +41113,7 @@
         <v>742.47200132330545</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2024</v>
       </c>
@@ -41120,7 +41125,7 @@
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2025</v>
       </c>
@@ -41132,22 +41137,22 @@
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2015</v>
       </c>
@@ -41180,7 +41185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2016</v>
       </c>
@@ -41213,7 +41218,7 @@
         <v>0.96710480409873656</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2017</v>
       </c>
@@ -41246,10 +41251,10 @@
         <v>1.0909978506793983</v>
       </c>
       <c r="I20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2018</v>
       </c>
@@ -41282,7 +41287,7 @@
         <v>1.2148908972600598</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2019</v>
       </c>
@@ -41315,7 +41320,7 @@
         <v>1.2417383155128119</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -41348,7 +41353,7 @@
         <v>1.2830423749645821</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2021</v>
       </c>
@@ -41381,7 +41386,7 @@
         <v>1.6309481596102684</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2022</v>
       </c>
@@ -41414,7 +41419,7 @@
         <v>1.4129892044608989</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2023</v>
       </c>
@@ -41447,7 +41452,7 @@
         <v>1.9531193101664841</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2024</v>
       </c>
@@ -41480,7 +41485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2025</v>
       </c>
@@ -41519,6 +41524,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004E32BC299DDA75418A481CE8C1C04767" ma:contentTypeVersion="10" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="0fa4796f6798a7b079311364fca30a32">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="03763a1d-3ef6-4dac-84db-711c24c35716" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ccd651f340b356ff6f610107a3061652" ns2:_="">
     <xsd:import namespace="03763a1d-3ef6-4dac-84db-711c24c35716"/>
@@ -41696,15 +41710,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -41716,13 +41721,37 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10537B3E-014A-469F-981F-8DE51CBD53A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0FB69B-9C77-4E2A-8594-F035F4CB67B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0FB69B-9C77-4E2A-8594-F035F4CB67B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10537B3E-014A-469F-981F-8DE51CBD53A5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="03763a1d-3ef6-4dac-84db-711c24c35716"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{953D09D3-C993-4E4F-8FAB-E2C355431566}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{953D09D3-C993-4E4F-8FAB-E2C355431566}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="03763a1d-3ef6-4dac-84db-711c24c35716"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>